--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B925"/>
+  <dimension ref="A1:B926"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7763,6 +7763,14 @@
         <v>4.86965</v>
       </c>
     </row>
+    <row r="926" spans="1:2">
+      <c r="A926" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B926">
+        <v>4.84211</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B926"/>
+  <dimension ref="A1:B927"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7771,6 +7771,14 @@
         <v>4.84211</v>
       </c>
     </row>
+    <row r="927" spans="1:2">
+      <c r="A927" s="2">
+        <v>46171</v>
+      </c>
+      <c r="B927">
+        <v>4.85786</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B927"/>
+  <dimension ref="A1:B928"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7779,6 +7779,14 @@
         <v>4.85786</v>
       </c>
     </row>
+    <row r="928" spans="1:2">
+      <c r="A928" s="2">
+        <v>46178</v>
+      </c>
+      <c r="B928">
+        <v>4.78426</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -357,7 +357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B928"/>
+  <dimension ref="A1:B929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7787,6 +7787,14 @@
         <v>4.78426</v>
       </c>
     </row>
+    <row r="929" spans="1:2">
+      <c r="A929" s="2">
+        <v>46185</v>
+      </c>
+      <c r="B929">
+        <v>4.76339</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -30,8 +30,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -47,7 +55,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -55,13 +63,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -357,22 +383,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B929"/>
+  <dimension ref="A1:B930"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>39696</v>
       </c>
       <c r="B2">
@@ -380,7 +406,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>39703</v>
       </c>
       <c r="B3">
@@ -388,7 +414,7 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>39710</v>
       </c>
       <c r="B4">
@@ -396,7 +422,7 @@
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>39717</v>
       </c>
       <c r="B5">
@@ -404,7 +430,7 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>39724</v>
       </c>
       <c r="B6">
@@ -412,7 +438,7 @@
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="2">
+      <c r="A7" s="3">
         <v>39731</v>
       </c>
       <c r="B7">
@@ -420,7 +446,7 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="2">
+      <c r="A8" s="3">
         <v>39738</v>
       </c>
       <c r="B8">
@@ -428,7 +454,7 @@
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="2">
+      <c r="A9" s="3">
         <v>39745</v>
       </c>
       <c r="B9">
@@ -436,7 +462,7 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="2">
+      <c r="A10" s="3">
         <v>39752</v>
       </c>
       <c r="B10">
@@ -444,7 +470,7 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2">
+      <c r="A11" s="3">
         <v>39759</v>
       </c>
       <c r="B11">
@@ -452,7 +478,7 @@
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2">
+      <c r="A12" s="3">
         <v>39766</v>
       </c>
       <c r="B12">
@@ -460,7 +486,7 @@
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2">
+      <c r="A13" s="3">
         <v>39773</v>
       </c>
       <c r="B13">
@@ -468,7 +494,7 @@
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2">
+      <c r="A14" s="3">
         <v>39780</v>
       </c>
       <c r="B14">
@@ -476,7 +502,7 @@
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2">
+      <c r="A15" s="3">
         <v>39787</v>
       </c>
       <c r="B15">
@@ -484,7 +510,7 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2">
+      <c r="A16" s="3">
         <v>39794</v>
       </c>
       <c r="B16">
@@ -492,7 +518,7 @@
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="2">
+      <c r="A17" s="3">
         <v>39801</v>
       </c>
       <c r="B17">
@@ -500,7 +526,7 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="2">
+      <c r="A18" s="3">
         <v>39808</v>
       </c>
       <c r="B18">
@@ -508,7 +534,7 @@
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>39815</v>
       </c>
       <c r="B19">
@@ -516,7 +542,7 @@
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>39822</v>
       </c>
       <c r="B20">
@@ -524,7 +550,7 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>39829</v>
       </c>
       <c r="B21">
@@ -532,7 +558,7 @@
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>39836</v>
       </c>
       <c r="B22">
@@ -540,7 +566,7 @@
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="2">
+      <c r="A23" s="3">
         <v>39843</v>
       </c>
       <c r="B23">
@@ -548,7 +574,7 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="2">
+      <c r="A24" s="3">
         <v>39850</v>
       </c>
       <c r="B24">
@@ -556,7 +582,7 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="2">
+      <c r="A25" s="3">
         <v>39857</v>
       </c>
       <c r="B25">
@@ -564,7 +590,7 @@
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="2">
+      <c r="A26" s="3">
         <v>39864</v>
       </c>
       <c r="B26">
@@ -572,7 +598,7 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="2">
+      <c r="A27" s="3">
         <v>39871</v>
       </c>
       <c r="B27">
@@ -580,7 +606,7 @@
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="2">
+      <c r="A28" s="3">
         <v>39878</v>
       </c>
       <c r="B28">
@@ -588,7 +614,7 @@
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="2">
+      <c r="A29" s="3">
         <v>39885</v>
       </c>
       <c r="B29">
@@ -596,7 +622,7 @@
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="2">
+      <c r="A30" s="3">
         <v>39892</v>
       </c>
       <c r="B30">
@@ -604,7 +630,7 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="2">
+      <c r="A31" s="3">
         <v>39899</v>
       </c>
       <c r="B31">
@@ -612,7 +638,7 @@
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="2">
+      <c r="A32" s="3">
         <v>39906</v>
       </c>
       <c r="B32">
@@ -620,7 +646,7 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="2">
+      <c r="A33" s="3">
         <v>39913</v>
       </c>
       <c r="B33">
@@ -628,7 +654,7 @@
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="2">
+      <c r="A34" s="3">
         <v>39920</v>
       </c>
       <c r="B34">
@@ -636,7 +662,7 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="2">
+      <c r="A35" s="3">
         <v>39927</v>
       </c>
       <c r="B35">
@@ -644,7 +670,7 @@
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="2">
+      <c r="A36" s="3">
         <v>39934</v>
       </c>
       <c r="B36">
@@ -652,7 +678,7 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="2">
+      <c r="A37" s="3">
         <v>39941</v>
       </c>
       <c r="B37">
@@ -660,7 +686,7 @@
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="2">
+      <c r="A38" s="3">
         <v>39948</v>
       </c>
       <c r="B38">
@@ -668,7 +694,7 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="2">
+      <c r="A39" s="3">
         <v>39955</v>
       </c>
       <c r="B39">
@@ -676,7 +702,7 @@
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="2">
+      <c r="A40" s="3">
         <v>39962</v>
       </c>
       <c r="B40">
@@ -684,7 +710,7 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="2">
+      <c r="A41" s="3">
         <v>39969</v>
       </c>
       <c r="B41">
@@ -692,7 +718,7 @@
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="2">
+      <c r="A42" s="3">
         <v>39976</v>
       </c>
       <c r="B42">
@@ -700,7 +726,7 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="2">
+      <c r="A43" s="3">
         <v>39983</v>
       </c>
       <c r="B43">
@@ -708,7 +734,7 @@
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="2">
+      <c r="A44" s="3">
         <v>39990</v>
       </c>
       <c r="B44">
@@ -716,7 +742,7 @@
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="2">
+      <c r="A45" s="3">
         <v>39997</v>
       </c>
       <c r="B45">
@@ -724,7 +750,7 @@
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="2">
+      <c r="A46" s="3">
         <v>40004</v>
       </c>
       <c r="B46">
@@ -732,7 +758,7 @@
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="2">
+      <c r="A47" s="3">
         <v>40011</v>
       </c>
       <c r="B47">
@@ -740,7 +766,7 @@
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="2">
+      <c r="A48" s="3">
         <v>40018</v>
       </c>
       <c r="B48">
@@ -748,7 +774,7 @@
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="2">
+      <c r="A49" s="3">
         <v>40025</v>
       </c>
       <c r="B49">
@@ -756,7 +782,7 @@
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="2">
+      <c r="A50" s="3">
         <v>40032</v>
       </c>
       <c r="B50">
@@ -764,7 +790,7 @@
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="2">
+      <c r="A51" s="3">
         <v>40039</v>
       </c>
       <c r="B51">
@@ -772,7 +798,7 @@
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="2">
+      <c r="A52" s="3">
         <v>40046</v>
       </c>
       <c r="B52">
@@ -780,7 +806,7 @@
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="2">
+      <c r="A53" s="3">
         <v>40053</v>
       </c>
       <c r="B53">
@@ -788,7 +814,7 @@
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="2">
+      <c r="A54" s="3">
         <v>40060</v>
       </c>
       <c r="B54">
@@ -796,7 +822,7 @@
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="2">
+      <c r="A55" s="3">
         <v>40067</v>
       </c>
       <c r="B55">
@@ -804,7 +830,7 @@
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="2">
+      <c r="A56" s="3">
         <v>40074</v>
       </c>
       <c r="B56">
@@ -812,7 +838,7 @@
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="2">
+      <c r="A57" s="3">
         <v>40081</v>
       </c>
       <c r="B57">
@@ -820,7 +846,7 @@
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="2">
+      <c r="A58" s="3">
         <v>40088</v>
       </c>
       <c r="B58">
@@ -828,7 +854,7 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2">
+      <c r="A59" s="3">
         <v>40095</v>
       </c>
       <c r="B59">
@@ -836,7 +862,7 @@
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="2">
+      <c r="A60" s="3">
         <v>40102</v>
       </c>
       <c r="B60">
@@ -844,7 +870,7 @@
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2">
+      <c r="A61" s="3">
         <v>40109</v>
       </c>
       <c r="B61">
@@ -852,7 +878,7 @@
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="2">
+      <c r="A62" s="3">
         <v>40116</v>
       </c>
       <c r="B62">
@@ -860,7 +886,7 @@
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2">
+      <c r="A63" s="3">
         <v>40123</v>
       </c>
       <c r="B63">
@@ -868,7 +894,7 @@
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="2">
+      <c r="A64" s="3">
         <v>40130</v>
       </c>
       <c r="B64">
@@ -876,7 +902,7 @@
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2">
+      <c r="A65" s="3">
         <v>40137</v>
       </c>
       <c r="B65">
@@ -884,7 +910,7 @@
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="2">
+      <c r="A66" s="3">
         <v>40144</v>
       </c>
       <c r="B66">
@@ -892,7 +918,7 @@
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2">
+      <c r="A67" s="3">
         <v>40151</v>
       </c>
       <c r="B67">
@@ -900,7 +926,7 @@
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="2">
+      <c r="A68" s="3">
         <v>40158</v>
       </c>
       <c r="B68">
@@ -908,7 +934,7 @@
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2">
+      <c r="A69" s="3">
         <v>40165</v>
       </c>
       <c r="B69">
@@ -916,7 +942,7 @@
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="2">
+      <c r="A70" s="3">
         <v>40172</v>
       </c>
       <c r="B70">
@@ -924,7 +950,7 @@
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2">
+      <c r="A71" s="3">
         <v>40179</v>
       </c>
       <c r="B71">
@@ -932,7 +958,7 @@
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="2">
+      <c r="A72" s="3">
         <v>40186</v>
       </c>
       <c r="B72">
@@ -940,7 +966,7 @@
       </c>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2">
+      <c r="A73" s="3">
         <v>40193</v>
       </c>
       <c r="B73">
@@ -948,7 +974,7 @@
       </c>
     </row>
     <row r="74" spans="1:2">
-      <c r="A74" s="2">
+      <c r="A74" s="3">
         <v>40200</v>
       </c>
       <c r="B74">
@@ -956,7 +982,7 @@
       </c>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2">
+      <c r="A75" s="3">
         <v>40207</v>
       </c>
       <c r="B75">
@@ -964,7 +990,7 @@
       </c>
     </row>
     <row r="76" spans="1:2">
-      <c r="A76" s="2">
+      <c r="A76" s="3">
         <v>40214</v>
       </c>
       <c r="B76">
@@ -972,7 +998,7 @@
       </c>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2">
+      <c r="A77" s="3">
         <v>40221</v>
       </c>
       <c r="B77">
@@ -980,7 +1006,7 @@
       </c>
     </row>
     <row r="78" spans="1:2">
-      <c r="A78" s="2">
+      <c r="A78" s="3">
         <v>40228</v>
       </c>
       <c r="B78">
@@ -988,7 +1014,7 @@
       </c>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2">
+      <c r="A79" s="3">
         <v>40235</v>
       </c>
       <c r="B79">
@@ -996,7 +1022,7 @@
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="2">
+      <c r="A80" s="3">
         <v>40242</v>
       </c>
       <c r="B80">
@@ -1004,7 +1030,7 @@
       </c>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2">
+      <c r="A81" s="3">
         <v>40249</v>
       </c>
       <c r="B81">
@@ -1012,7 +1038,7 @@
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="2">
+      <c r="A82" s="3">
         <v>40256</v>
       </c>
       <c r="B82">
@@ -1020,7 +1046,7 @@
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2">
+      <c r="A83" s="3">
         <v>40263</v>
       </c>
       <c r="B83">
@@ -1028,7 +1054,7 @@
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="2">
+      <c r="A84" s="3">
         <v>40270</v>
       </c>
       <c r="B84">
@@ -1036,7 +1062,7 @@
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2">
+      <c r="A85" s="3">
         <v>40277</v>
       </c>
       <c r="B85">
@@ -1044,7 +1070,7 @@
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="2">
+      <c r="A86" s="3">
         <v>40284</v>
       </c>
       <c r="B86">
@@ -1052,7 +1078,7 @@
       </c>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2">
+      <c r="A87" s="3">
         <v>40291</v>
       </c>
       <c r="B87">
@@ -1060,7 +1086,7 @@
       </c>
     </row>
     <row r="88" spans="1:2">
-      <c r="A88" s="2">
+      <c r="A88" s="3">
         <v>40298</v>
       </c>
       <c r="B88">
@@ -1068,7 +1094,7 @@
       </c>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2">
+      <c r="A89" s="3">
         <v>40305</v>
       </c>
       <c r="B89">
@@ -1076,7 +1102,7 @@
       </c>
     </row>
     <row r="90" spans="1:2">
-      <c r="A90" s="2">
+      <c r="A90" s="3">
         <v>40312</v>
       </c>
       <c r="B90">
@@ -1084,7 +1110,7 @@
       </c>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2">
+      <c r="A91" s="3">
         <v>40319</v>
       </c>
       <c r="B91">
@@ -1092,7 +1118,7 @@
       </c>
     </row>
     <row r="92" spans="1:2">
-      <c r="A92" s="2">
+      <c r="A92" s="3">
         <v>40326</v>
       </c>
       <c r="B92">
@@ -1100,7 +1126,7 @@
       </c>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2">
+      <c r="A93" s="3">
         <v>40333</v>
       </c>
       <c r="B93">
@@ -1108,7 +1134,7 @@
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="2">
+      <c r="A94" s="3">
         <v>40340</v>
       </c>
       <c r="B94">
@@ -1116,7 +1142,7 @@
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2">
+      <c r="A95" s="3">
         <v>40347</v>
       </c>
       <c r="B95">
@@ -1124,7 +1150,7 @@
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="2">
+      <c r="A96" s="3">
         <v>40354</v>
       </c>
       <c r="B96">
@@ -1132,7 +1158,7 @@
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2">
+      <c r="A97" s="3">
         <v>40361</v>
       </c>
       <c r="B97">
@@ -1140,7 +1166,7 @@
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="2">
+      <c r="A98" s="3">
         <v>40368</v>
       </c>
       <c r="B98">
@@ -1148,7 +1174,7 @@
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2">
+      <c r="A99" s="3">
         <v>40375</v>
       </c>
       <c r="B99">
@@ -1156,7 +1182,7 @@
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="2">
+      <c r="A100" s="3">
         <v>40382</v>
       </c>
       <c r="B100">
@@ -1164,7 +1190,7 @@
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2">
+      <c r="A101" s="3">
         <v>40389</v>
       </c>
       <c r="B101">
@@ -1172,7 +1198,7 @@
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="2">
+      <c r="A102" s="3">
         <v>40396</v>
       </c>
       <c r="B102">
@@ -1180,7 +1206,7 @@
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2">
+      <c r="A103" s="3">
         <v>40403</v>
       </c>
       <c r="B103">
@@ -1188,7 +1214,7 @@
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="2">
+      <c r="A104" s="3">
         <v>40410</v>
       </c>
       <c r="B104">
@@ -1196,7 +1222,7 @@
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="2">
+      <c r="A105" s="3">
         <v>40417</v>
       </c>
       <c r="B105">
@@ -1204,7 +1230,7 @@
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="2">
+      <c r="A106" s="3">
         <v>40424</v>
       </c>
       <c r="B106">
@@ -1212,7 +1238,7 @@
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="2">
+      <c r="A107" s="3">
         <v>40431</v>
       </c>
       <c r="B107">
@@ -1220,7 +1246,7 @@
       </c>
     </row>
     <row r="108" spans="1:2">
-      <c r="A108" s="2">
+      <c r="A108" s="3">
         <v>40438</v>
       </c>
       <c r="B108">
@@ -1228,7 +1254,7 @@
       </c>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="2">
+      <c r="A109" s="3">
         <v>40445</v>
       </c>
       <c r="B109">
@@ -1236,7 +1262,7 @@
       </c>
     </row>
     <row r="110" spans="1:2">
-      <c r="A110" s="2">
+      <c r="A110" s="3">
         <v>40452</v>
       </c>
       <c r="B110">
@@ -1244,7 +1270,7 @@
       </c>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="2">
+      <c r="A111" s="3">
         <v>40459</v>
       </c>
       <c r="B111">
@@ -1252,7 +1278,7 @@
       </c>
     </row>
     <row r="112" spans="1:2">
-      <c r="A112" s="2">
+      <c r="A112" s="3">
         <v>40466</v>
       </c>
       <c r="B112">
@@ -1260,7 +1286,7 @@
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="2">
+      <c r="A113" s="3">
         <v>40473</v>
       </c>
       <c r="B113">
@@ -1268,7 +1294,7 @@
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="2">
+      <c r="A114" s="3">
         <v>40480</v>
       </c>
       <c r="B114">
@@ -1276,7 +1302,7 @@
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="2">
+      <c r="A115" s="3">
         <v>40487</v>
       </c>
       <c r="B115">
@@ -1284,7 +1310,7 @@
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="2">
+      <c r="A116" s="3">
         <v>40494</v>
       </c>
       <c r="B116">
@@ -1292,7 +1318,7 @@
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="2">
+      <c r="A117" s="3">
         <v>40501</v>
       </c>
       <c r="B117">
@@ -1300,7 +1326,7 @@
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="2">
+      <c r="A118" s="3">
         <v>40508</v>
       </c>
       <c r="B118">
@@ -1308,7 +1334,7 @@
       </c>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="2">
+      <c r="A119" s="3">
         <v>40515</v>
       </c>
       <c r="B119">
@@ -1316,7 +1342,7 @@
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" s="2">
+      <c r="A120" s="3">
         <v>40522</v>
       </c>
       <c r="B120">
@@ -1324,7 +1350,7 @@
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="2">
+      <c r="A121" s="3">
         <v>40529</v>
       </c>
       <c r="B121">
@@ -1332,7 +1358,7 @@
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="2">
+      <c r="A122" s="3">
         <v>40536</v>
       </c>
       <c r="B122">
@@ -1340,7 +1366,7 @@
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="2">
+      <c r="A123" s="3">
         <v>40543</v>
       </c>
       <c r="B123">
@@ -1348,7 +1374,7 @@
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="2">
+      <c r="A124" s="3">
         <v>40550</v>
       </c>
       <c r="B124">
@@ -1356,7 +1382,7 @@
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="2">
+      <c r="A125" s="3">
         <v>40557</v>
       </c>
       <c r="B125">
@@ -1364,7 +1390,7 @@
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="2">
+      <c r="A126" s="3">
         <v>40564</v>
       </c>
       <c r="B126">
@@ -1372,7 +1398,7 @@
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="2">
+      <c r="A127" s="3">
         <v>40571</v>
       </c>
       <c r="B127">
@@ -1380,7 +1406,7 @@
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="2">
+      <c r="A128" s="3">
         <v>40578</v>
       </c>
       <c r="B128">
@@ -1388,7 +1414,7 @@
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2">
+      <c r="A129" s="3">
         <v>40585</v>
       </c>
       <c r="B129">
@@ -1396,7 +1422,7 @@
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="2">
+      <c r="A130" s="3">
         <v>40592</v>
       </c>
       <c r="B130">
@@ -1404,7 +1430,7 @@
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="2">
+      <c r="A131" s="3">
         <v>40599</v>
       </c>
       <c r="B131">
@@ -1412,7 +1438,7 @@
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="2">
+      <c r="A132" s="3">
         <v>40606</v>
       </c>
       <c r="B132">
@@ -1420,7 +1446,7 @@
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2">
+      <c r="A133" s="3">
         <v>40613</v>
       </c>
       <c r="B133">
@@ -1428,7 +1454,7 @@
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="2">
+      <c r="A134" s="3">
         <v>40620</v>
       </c>
       <c r="B134">
@@ -1436,7 +1462,7 @@
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2">
+      <c r="A135" s="3">
         <v>40627</v>
       </c>
       <c r="B135">
@@ -1444,7 +1470,7 @@
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="2">
+      <c r="A136" s="3">
         <v>40634</v>
       </c>
       <c r="B136">
@@ -1452,7 +1478,7 @@
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2">
+      <c r="A137" s="3">
         <v>40641</v>
       </c>
       <c r="B137">
@@ -1460,7 +1486,7 @@
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2">
+      <c r="A138" s="3">
         <v>40648</v>
       </c>
       <c r="B138">
@@ -1468,7 +1494,7 @@
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2">
+      <c r="A139" s="3">
         <v>40655</v>
       </c>
       <c r="B139">
@@ -1476,7 +1502,7 @@
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="2">
+      <c r="A140" s="3">
         <v>40662</v>
       </c>
       <c r="B140">
@@ -1484,7 +1510,7 @@
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="2">
+      <c r="A141" s="3">
         <v>40669</v>
       </c>
       <c r="B141">
@@ -1492,7 +1518,7 @@
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="2">
+      <c r="A142" s="3">
         <v>40676</v>
       </c>
       <c r="B142">
@@ -1500,7 +1526,7 @@
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="2">
+      <c r="A143" s="3">
         <v>40683</v>
       </c>
       <c r="B143">
@@ -1508,7 +1534,7 @@
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="2">
+      <c r="A144" s="3">
         <v>40690</v>
       </c>
       <c r="B144">
@@ -1516,7 +1542,7 @@
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="2">
+      <c r="A145" s="3">
         <v>40697</v>
       </c>
       <c r="B145">
@@ -1524,7 +1550,7 @@
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="2">
+      <c r="A146" s="3">
         <v>40704</v>
       </c>
       <c r="B146">
@@ -1532,7 +1558,7 @@
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="2">
+      <c r="A147" s="3">
         <v>40711</v>
       </c>
       <c r="B147">
@@ -1540,7 +1566,7 @@
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="2">
+      <c r="A148" s="3">
         <v>40718</v>
       </c>
       <c r="B148">
@@ -1548,7 +1574,7 @@
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="2">
+      <c r="A149" s="3">
         <v>40725</v>
       </c>
       <c r="B149">
@@ -1556,7 +1582,7 @@
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="2">
+      <c r="A150" s="3">
         <v>40732</v>
       </c>
       <c r="B150">
@@ -1564,7 +1590,7 @@
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="2">
+      <c r="A151" s="3">
         <v>40739</v>
       </c>
       <c r="B151">
@@ -1572,7 +1598,7 @@
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="2">
+      <c r="A152" s="3">
         <v>40746</v>
       </c>
       <c r="B152">
@@ -1580,7 +1606,7 @@
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="2">
+      <c r="A153" s="3">
         <v>40753</v>
       </c>
       <c r="B153">
@@ -1588,7 +1614,7 @@
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="2">
+      <c r="A154" s="3">
         <v>40760</v>
       </c>
       <c r="B154">
@@ -1596,7 +1622,7 @@
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="2">
+      <c r="A155" s="3">
         <v>40767</v>
       </c>
       <c r="B155">
@@ -1604,7 +1630,7 @@
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="2">
+      <c r="A156" s="3">
         <v>40774</v>
       </c>
       <c r="B156">
@@ -1612,7 +1638,7 @@
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="2">
+      <c r="A157" s="3">
         <v>40781</v>
       </c>
       <c r="B157">
@@ -1620,7 +1646,7 @@
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="2">
+      <c r="A158" s="3">
         <v>40788</v>
       </c>
       <c r="B158">
@@ -1628,7 +1654,7 @@
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="2">
+      <c r="A159" s="3">
         <v>40795</v>
       </c>
       <c r="B159">
@@ -1636,7 +1662,7 @@
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="2">
+      <c r="A160" s="3">
         <v>40802</v>
       </c>
       <c r="B160">
@@ -1644,7 +1670,7 @@
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="2">
+      <c r="A161" s="3">
         <v>40809</v>
       </c>
       <c r="B161">
@@ -1652,7 +1678,7 @@
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="2">
+      <c r="A162" s="3">
         <v>40816</v>
       </c>
       <c r="B162">
@@ -1660,7 +1686,7 @@
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="2">
+      <c r="A163" s="3">
         <v>40823</v>
       </c>
       <c r="B163">
@@ -1668,7 +1694,7 @@
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="2">
+      <c r="A164" s="3">
         <v>40830</v>
       </c>
       <c r="B164">
@@ -1676,7 +1702,7 @@
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="2">
+      <c r="A165" s="3">
         <v>40837</v>
       </c>
       <c r="B165">
@@ -1684,7 +1710,7 @@
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="2">
+      <c r="A166" s="3">
         <v>40844</v>
       </c>
       <c r="B166">
@@ -1692,7 +1718,7 @@
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="2">
+      <c r="A167" s="3">
         <v>40851</v>
       </c>
       <c r="B167">
@@ -1700,7 +1726,7 @@
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="2">
+      <c r="A168" s="3">
         <v>40858</v>
       </c>
       <c r="B168">
@@ -1708,7 +1734,7 @@
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="2">
+      <c r="A169" s="3">
         <v>40865</v>
       </c>
       <c r="B169">
@@ -1716,7 +1742,7 @@
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="2">
+      <c r="A170" s="3">
         <v>40872</v>
       </c>
       <c r="B170">
@@ -1724,7 +1750,7 @@
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="2">
+      <c r="A171" s="3">
         <v>40879</v>
       </c>
       <c r="B171">
@@ -1732,7 +1758,7 @@
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="2">
+      <c r="A172" s="3">
         <v>40886</v>
       </c>
       <c r="B172">
@@ -1740,7 +1766,7 @@
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="2">
+      <c r="A173" s="3">
         <v>40893</v>
       </c>
       <c r="B173">
@@ -1748,7 +1774,7 @@
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="2">
+      <c r="A174" s="3">
         <v>40900</v>
       </c>
       <c r="B174">
@@ -1756,7 +1782,7 @@
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="2">
+      <c r="A175" s="3">
         <v>40907</v>
       </c>
       <c r="B175">
@@ -1764,7 +1790,7 @@
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="2">
+      <c r="A176" s="3">
         <v>40914</v>
       </c>
       <c r="B176">
@@ -1772,7 +1798,7 @@
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="2">
+      <c r="A177" s="3">
         <v>40921</v>
       </c>
       <c r="B177">
@@ -1780,7 +1806,7 @@
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="2">
+      <c r="A178" s="3">
         <v>40928</v>
       </c>
       <c r="B178">
@@ -1788,7 +1814,7 @@
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="2">
+      <c r="A179" s="3">
         <v>40935</v>
       </c>
       <c r="B179">
@@ -1796,7 +1822,7 @@
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="2">
+      <c r="A180" s="3">
         <v>40942</v>
       </c>
       <c r="B180">
@@ -1804,7 +1830,7 @@
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="2">
+      <c r="A181" s="3">
         <v>40949</v>
       </c>
       <c r="B181">
@@ -1812,7 +1838,7 @@
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="2">
+      <c r="A182" s="3">
         <v>40956</v>
       </c>
       <c r="B182">
@@ -1820,7 +1846,7 @@
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="2">
+      <c r="A183" s="3">
         <v>40963</v>
       </c>
       <c r="B183">
@@ -1828,7 +1854,7 @@
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="2">
+      <c r="A184" s="3">
         <v>40970</v>
       </c>
       <c r="B184">
@@ -1836,7 +1862,7 @@
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="2">
+      <c r="A185" s="3">
         <v>40977</v>
       </c>
       <c r="B185">
@@ -1844,7 +1870,7 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="2">
+      <c r="A186" s="3">
         <v>40984</v>
       </c>
       <c r="B186">
@@ -1852,7 +1878,7 @@
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="2">
+      <c r="A187" s="3">
         <v>40991</v>
       </c>
       <c r="B187">
@@ -1860,7 +1886,7 @@
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="2">
+      <c r="A188" s="3">
         <v>40998</v>
       </c>
       <c r="B188">
@@ -1868,7 +1894,7 @@
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="2">
+      <c r="A189" s="3">
         <v>41005</v>
       </c>
       <c r="B189">
@@ -1876,7 +1902,7 @@
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="2">
+      <c r="A190" s="3">
         <v>41012</v>
       </c>
       <c r="B190">
@@ -1884,7 +1910,7 @@
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="2">
+      <c r="A191" s="3">
         <v>41019</v>
       </c>
       <c r="B191">
@@ -1892,7 +1918,7 @@
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="2">
+      <c r="A192" s="3">
         <v>41026</v>
       </c>
       <c r="B192">
@@ -1900,7 +1926,7 @@
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="2">
+      <c r="A193" s="3">
         <v>41033</v>
       </c>
       <c r="B193">
@@ -1908,7 +1934,7 @@
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="2">
+      <c r="A194" s="3">
         <v>41040</v>
       </c>
       <c r="B194">
@@ -1916,7 +1942,7 @@
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="2">
+      <c r="A195" s="3">
         <v>41047</v>
       </c>
       <c r="B195">
@@ -1924,7 +1950,7 @@
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="2">
+      <c r="A196" s="3">
         <v>41054</v>
       </c>
       <c r="B196">
@@ -1932,7 +1958,7 @@
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="2">
+      <c r="A197" s="3">
         <v>41061</v>
       </c>
       <c r="B197">
@@ -1940,7 +1966,7 @@
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="2">
+      <c r="A198" s="3">
         <v>41068</v>
       </c>
       <c r="B198">
@@ -1948,7 +1974,7 @@
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="2">
+      <c r="A199" s="3">
         <v>41075</v>
       </c>
       <c r="B199">
@@ -1956,7 +1982,7 @@
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="2">
+      <c r="A200" s="3">
         <v>41082</v>
       </c>
       <c r="B200">
@@ -1964,7 +1990,7 @@
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="2">
+      <c r="A201" s="3">
         <v>41089</v>
       </c>
       <c r="B201">
@@ -1972,7 +1998,7 @@
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="2">
+      <c r="A202" s="3">
         <v>41096</v>
       </c>
       <c r="B202">
@@ -1980,7 +2006,7 @@
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="2">
+      <c r="A203" s="3">
         <v>41103</v>
       </c>
       <c r="B203">
@@ -1988,7 +2014,7 @@
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="2">
+      <c r="A204" s="3">
         <v>41110</v>
       </c>
       <c r="B204">
@@ -1996,7 +2022,7 @@
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="2">
+      <c r="A205" s="3">
         <v>41117</v>
       </c>
       <c r="B205">
@@ -2004,7 +2030,7 @@
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="2">
+      <c r="A206" s="3">
         <v>41124</v>
       </c>
       <c r="B206">
@@ -2012,7 +2038,7 @@
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="2">
+      <c r="A207" s="3">
         <v>41131</v>
       </c>
       <c r="B207">
@@ -2020,7 +2046,7 @@
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="2">
+      <c r="A208" s="3">
         <v>41138</v>
       </c>
       <c r="B208">
@@ -2028,7 +2054,7 @@
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="2">
+      <c r="A209" s="3">
         <v>41145</v>
       </c>
       <c r="B209">
@@ -2036,7 +2062,7 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="2">
+      <c r="A210" s="3">
         <v>41152</v>
       </c>
       <c r="B210">
@@ -2044,7 +2070,7 @@
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="2">
+      <c r="A211" s="3">
         <v>41159</v>
       </c>
       <c r="B211">
@@ -2052,7 +2078,7 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="2">
+      <c r="A212" s="3">
         <v>41166</v>
       </c>
       <c r="B212">
@@ -2060,7 +2086,7 @@
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="2">
+      <c r="A213" s="3">
         <v>41173</v>
       </c>
       <c r="B213">
@@ -2068,7 +2094,7 @@
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="2">
+      <c r="A214" s="3">
         <v>41180</v>
       </c>
       <c r="B214">
@@ -2076,7 +2102,7 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="2">
+      <c r="A215" s="3">
         <v>41187</v>
       </c>
       <c r="B215">
@@ -2084,7 +2110,7 @@
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="2">
+      <c r="A216" s="3">
         <v>41194</v>
       </c>
       <c r="B216">
@@ -2092,7 +2118,7 @@
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="2">
+      <c r="A217" s="3">
         <v>41201</v>
       </c>
       <c r="B217">
@@ -2100,7 +2126,7 @@
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="2">
+      <c r="A218" s="3">
         <v>41208</v>
       </c>
       <c r="B218">
@@ -2108,7 +2134,7 @@
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="2">
+      <c r="A219" s="3">
         <v>41215</v>
       </c>
       <c r="B219">
@@ -2116,7 +2142,7 @@
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="2">
+      <c r="A220" s="3">
         <v>41222</v>
       </c>
       <c r="B220">
@@ -2124,7 +2150,7 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="2">
+      <c r="A221" s="3">
         <v>41229</v>
       </c>
       <c r="B221">
@@ -2132,7 +2158,7 @@
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="2">
+      <c r="A222" s="3">
         <v>41236</v>
       </c>
       <c r="B222">
@@ -2140,7 +2166,7 @@
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="2">
+      <c r="A223" s="3">
         <v>41243</v>
       </c>
       <c r="B223">
@@ -2148,7 +2174,7 @@
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="2">
+      <c r="A224" s="3">
         <v>41250</v>
       </c>
       <c r="B224">
@@ -2156,7 +2182,7 @@
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="2">
+      <c r="A225" s="3">
         <v>41257</v>
       </c>
       <c r="B225">
@@ -2164,7 +2190,7 @@
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="2">
+      <c r="A226" s="3">
         <v>41264</v>
       </c>
       <c r="B226">
@@ -2172,7 +2198,7 @@
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="2">
+      <c r="A227" s="3">
         <v>41271</v>
       </c>
       <c r="B227">
@@ -2180,7 +2206,7 @@
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="2">
+      <c r="A228" s="3">
         <v>41278</v>
       </c>
       <c r="B228">
@@ -2188,7 +2214,7 @@
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="2">
+      <c r="A229" s="3">
         <v>41285</v>
       </c>
       <c r="B229">
@@ -2196,7 +2222,7 @@
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="2">
+      <c r="A230" s="3">
         <v>41292</v>
       </c>
       <c r="B230">
@@ -2204,7 +2230,7 @@
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="2">
+      <c r="A231" s="3">
         <v>41299</v>
       </c>
       <c r="B231">
@@ -2212,7 +2238,7 @@
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="2">
+      <c r="A232" s="3">
         <v>41306</v>
       </c>
       <c r="B232">
@@ -2220,7 +2246,7 @@
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="2">
+      <c r="A233" s="3">
         <v>41313</v>
       </c>
       <c r="B233">
@@ -2228,7 +2254,7 @@
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="2">
+      <c r="A234" s="3">
         <v>41320</v>
       </c>
       <c r="B234">
@@ -2236,7 +2262,7 @@
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="2">
+      <c r="A235" s="3">
         <v>41327</v>
       </c>
       <c r="B235">
@@ -2244,7 +2270,7 @@
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="2">
+      <c r="A236" s="3">
         <v>41334</v>
       </c>
       <c r="B236">
@@ -2252,7 +2278,7 @@
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="2">
+      <c r="A237" s="3">
         <v>41341</v>
       </c>
       <c r="B237">
@@ -2260,7 +2286,7 @@
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="2">
+      <c r="A238" s="3">
         <v>41348</v>
       </c>
       <c r="B238">
@@ -2268,7 +2294,7 @@
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="2">
+      <c r="A239" s="3">
         <v>41355</v>
       </c>
       <c r="B239">
@@ -2276,7 +2302,7 @@
       </c>
     </row>
     <row r="240" spans="1:2">
-      <c r="A240" s="2">
+      <c r="A240" s="3">
         <v>41362</v>
       </c>
       <c r="B240">
@@ -2284,7 +2310,7 @@
       </c>
     </row>
     <row r="241" spans="1:2">
-      <c r="A241" s="2">
+      <c r="A241" s="3">
         <v>41369</v>
       </c>
       <c r="B241">
@@ -2292,7 +2318,7 @@
       </c>
     </row>
     <row r="242" spans="1:2">
-      <c r="A242" s="2">
+      <c r="A242" s="3">
         <v>41376</v>
       </c>
       <c r="B242">
@@ -2300,7 +2326,7 @@
       </c>
     </row>
     <row r="243" spans="1:2">
-      <c r="A243" s="2">
+      <c r="A243" s="3">
         <v>41383</v>
       </c>
       <c r="B243">
@@ -2308,7 +2334,7 @@
       </c>
     </row>
     <row r="244" spans="1:2">
-      <c r="A244" s="2">
+      <c r="A244" s="3">
         <v>41390</v>
       </c>
       <c r="B244">
@@ -2316,7 +2342,7 @@
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="2">
+      <c r="A245" s="3">
         <v>41397</v>
       </c>
       <c r="B245">
@@ -2324,7 +2350,7 @@
       </c>
     </row>
     <row r="246" spans="1:2">
-      <c r="A246" s="2">
+      <c r="A246" s="3">
         <v>41404</v>
       </c>
       <c r="B246">
@@ -2332,7 +2358,7 @@
       </c>
     </row>
     <row r="247" spans="1:2">
-      <c r="A247" s="2">
+      <c r="A247" s="3">
         <v>41411</v>
       </c>
       <c r="B247">
@@ -2340,7 +2366,7 @@
       </c>
     </row>
     <row r="248" spans="1:2">
-      <c r="A248" s="2">
+      <c r="A248" s="3">
         <v>41418</v>
       </c>
       <c r="B248">
@@ -2348,7 +2374,7 @@
       </c>
     </row>
     <row r="249" spans="1:2">
-      <c r="A249" s="2">
+      <c r="A249" s="3">
         <v>41425</v>
       </c>
       <c r="B249">
@@ -2356,7 +2382,7 @@
       </c>
     </row>
     <row r="250" spans="1:2">
-      <c r="A250" s="2">
+      <c r="A250" s="3">
         <v>41432</v>
       </c>
       <c r="B250">
@@ -2364,7 +2390,7 @@
       </c>
     </row>
     <row r="251" spans="1:2">
-      <c r="A251" s="2">
+      <c r="A251" s="3">
         <v>41439</v>
       </c>
       <c r="B251">
@@ -2372,7 +2398,7 @@
       </c>
     </row>
     <row r="252" spans="1:2">
-      <c r="A252" s="2">
+      <c r="A252" s="3">
         <v>41446</v>
       </c>
       <c r="B252">
@@ -2380,7 +2406,7 @@
       </c>
     </row>
     <row r="253" spans="1:2">
-      <c r="A253" s="2">
+      <c r="A253" s="3">
         <v>41453</v>
       </c>
       <c r="B253">
@@ -2388,7 +2414,7 @@
       </c>
     </row>
     <row r="254" spans="1:2">
-      <c r="A254" s="2">
+      <c r="A254" s="3">
         <v>41460</v>
       </c>
       <c r="B254">
@@ -2396,7 +2422,7 @@
       </c>
     </row>
     <row r="255" spans="1:2">
-      <c r="A255" s="2">
+      <c r="A255" s="3">
         <v>41467</v>
       </c>
       <c r="B255">
@@ -2404,7 +2430,7 @@
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="2">
+      <c r="A256" s="3">
         <v>41474</v>
       </c>
       <c r="B256">
@@ -2412,7 +2438,7 @@
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="2">
+      <c r="A257" s="3">
         <v>41481</v>
       </c>
       <c r="B257">
@@ -2420,7 +2446,7 @@
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="2">
+      <c r="A258" s="3">
         <v>41488</v>
       </c>
       <c r="B258">
@@ -2428,7 +2454,7 @@
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="2">
+      <c r="A259" s="3">
         <v>41495</v>
       </c>
       <c r="B259">
@@ -2436,7 +2462,7 @@
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="2">
+      <c r="A260" s="3">
         <v>41502</v>
       </c>
       <c r="B260">
@@ -2444,7 +2470,7 @@
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="2">
+      <c r="A261" s="3">
         <v>41509</v>
       </c>
       <c r="B261">
@@ -2452,7 +2478,7 @@
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="2">
+      <c r="A262" s="3">
         <v>41516</v>
       </c>
       <c r="B262">
@@ -2460,7 +2486,7 @@
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="2">
+      <c r="A263" s="3">
         <v>41523</v>
       </c>
       <c r="B263">
@@ -2468,7 +2494,7 @@
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="2">
+      <c r="A264" s="3">
         <v>41530</v>
       </c>
       <c r="B264">
@@ -2476,7 +2502,7 @@
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="2">
+      <c r="A265" s="3">
         <v>41537</v>
       </c>
       <c r="B265">
@@ -2484,7 +2510,7 @@
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="2">
+      <c r="A266" s="3">
         <v>41544</v>
       </c>
       <c r="B266">
@@ -2492,7 +2518,7 @@
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="2">
+      <c r="A267" s="3">
         <v>41551</v>
       </c>
       <c r="B267">
@@ -2500,7 +2526,7 @@
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="2">
+      <c r="A268" s="3">
         <v>41558</v>
       </c>
       <c r="B268">
@@ -2508,7 +2534,7 @@
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="2">
+      <c r="A269" s="3">
         <v>41565</v>
       </c>
       <c r="B269">
@@ -2516,7 +2542,7 @@
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="2">
+      <c r="A270" s="3">
         <v>41572</v>
       </c>
       <c r="B270">
@@ -2524,7 +2550,7 @@
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="2">
+      <c r="A271" s="3">
         <v>41579</v>
       </c>
       <c r="B271">
@@ -2532,7 +2558,7 @@
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="2">
+      <c r="A272" s="3">
         <v>41586</v>
       </c>
       <c r="B272">
@@ -2540,7 +2566,7 @@
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="2">
+      <c r="A273" s="3">
         <v>41593</v>
       </c>
       <c r="B273">
@@ -2548,7 +2574,7 @@
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="2">
+      <c r="A274" s="3">
         <v>41600</v>
       </c>
       <c r="B274">
@@ -2556,7 +2582,7 @@
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="2">
+      <c r="A275" s="3">
         <v>41607</v>
       </c>
       <c r="B275">
@@ -2564,7 +2590,7 @@
       </c>
     </row>
     <row r="276" spans="1:2">
-      <c r="A276" s="2">
+      <c r="A276" s="3">
         <v>41614</v>
       </c>
       <c r="B276">
@@ -2572,7 +2598,7 @@
       </c>
     </row>
     <row r="277" spans="1:2">
-      <c r="A277" s="2">
+      <c r="A277" s="3">
         <v>41621</v>
       </c>
       <c r="B277">
@@ -2580,7 +2606,7 @@
       </c>
     </row>
     <row r="278" spans="1:2">
-      <c r="A278" s="2">
+      <c r="A278" s="3">
         <v>41628</v>
       </c>
       <c r="B278">
@@ -2588,7 +2614,7 @@
       </c>
     </row>
     <row r="279" spans="1:2">
-      <c r="A279" s="2">
+      <c r="A279" s="3">
         <v>41635</v>
       </c>
       <c r="B279">
@@ -2596,7 +2622,7 @@
       </c>
     </row>
     <row r="280" spans="1:2">
-      <c r="A280" s="2">
+      <c r="A280" s="3">
         <v>41642</v>
       </c>
       <c r="B280">
@@ -2604,7 +2630,7 @@
       </c>
     </row>
     <row r="281" spans="1:2">
-      <c r="A281" s="2">
+      <c r="A281" s="3">
         <v>41649</v>
       </c>
       <c r="B281">
@@ -2612,7 +2638,7 @@
       </c>
     </row>
     <row r="282" spans="1:2">
-      <c r="A282" s="2">
+      <c r="A282" s="3">
         <v>41656</v>
       </c>
       <c r="B282">
@@ -2620,7 +2646,7 @@
       </c>
     </row>
     <row r="283" spans="1:2">
-      <c r="A283" s="2">
+      <c r="A283" s="3">
         <v>41663</v>
       </c>
       <c r="B283">
@@ -2628,7 +2654,7 @@
       </c>
     </row>
     <row r="284" spans="1:2">
-      <c r="A284" s="2">
+      <c r="A284" s="3">
         <v>41670</v>
       </c>
       <c r="B284">
@@ -2636,7 +2662,7 @@
       </c>
     </row>
     <row r="285" spans="1:2">
-      <c r="A285" s="2">
+      <c r="A285" s="3">
         <v>41677</v>
       </c>
       <c r="B285">
@@ -2644,7 +2670,7 @@
       </c>
     </row>
     <row r="286" spans="1:2">
-      <c r="A286" s="2">
+      <c r="A286" s="3">
         <v>41684</v>
       </c>
       <c r="B286">
@@ -2652,7 +2678,7 @@
       </c>
     </row>
     <row r="287" spans="1:2">
-      <c r="A287" s="2">
+      <c r="A287" s="3">
         <v>41691</v>
       </c>
       <c r="B287">
@@ -2660,7 +2686,7 @@
       </c>
     </row>
     <row r="288" spans="1:2">
-      <c r="A288" s="2">
+      <c r="A288" s="3">
         <v>41698</v>
       </c>
       <c r="B288">
@@ -2668,7 +2694,7 @@
       </c>
     </row>
     <row r="289" spans="1:2">
-      <c r="A289" s="2">
+      <c r="A289" s="3">
         <v>41705</v>
       </c>
       <c r="B289">
@@ -2676,7 +2702,7 @@
       </c>
     </row>
     <row r="290" spans="1:2">
-      <c r="A290" s="2">
+      <c r="A290" s="3">
         <v>41712</v>
       </c>
       <c r="B290">
@@ -2684,7 +2710,7 @@
       </c>
     </row>
     <row r="291" spans="1:2">
-      <c r="A291" s="2">
+      <c r="A291" s="3">
         <v>41719</v>
       </c>
       <c r="B291">
@@ -2692,7 +2718,7 @@
       </c>
     </row>
     <row r="292" spans="1:2">
-      <c r="A292" s="2">
+      <c r="A292" s="3">
         <v>41726</v>
       </c>
       <c r="B292">
@@ -2700,7 +2726,7 @@
       </c>
     </row>
     <row r="293" spans="1:2">
-      <c r="A293" s="2">
+      <c r="A293" s="3">
         <v>41733</v>
       </c>
       <c r="B293">
@@ -2708,7 +2734,7 @@
       </c>
     </row>
     <row r="294" spans="1:2">
-      <c r="A294" s="2">
+      <c r="A294" s="3">
         <v>41740</v>
       </c>
       <c r="B294">
@@ -2716,7 +2742,7 @@
       </c>
     </row>
     <row r="295" spans="1:2">
-      <c r="A295" s="2">
+      <c r="A295" s="3">
         <v>41747</v>
       </c>
       <c r="B295">
@@ -2724,7 +2750,7 @@
       </c>
     </row>
     <row r="296" spans="1:2">
-      <c r="A296" s="2">
+      <c r="A296" s="3">
         <v>41754</v>
       </c>
       <c r="B296">
@@ -2732,7 +2758,7 @@
       </c>
     </row>
     <row r="297" spans="1:2">
-      <c r="A297" s="2">
+      <c r="A297" s="3">
         <v>41761</v>
       </c>
       <c r="B297">
@@ -2740,7 +2766,7 @@
       </c>
     </row>
     <row r="298" spans="1:2">
-      <c r="A298" s="2">
+      <c r="A298" s="3">
         <v>41768</v>
       </c>
       <c r="B298">
@@ -2748,7 +2774,7 @@
       </c>
     </row>
     <row r="299" spans="1:2">
-      <c r="A299" s="2">
+      <c r="A299" s="3">
         <v>41775</v>
       </c>
       <c r="B299">
@@ -2756,7 +2782,7 @@
       </c>
     </row>
     <row r="300" spans="1:2">
-      <c r="A300" s="2">
+      <c r="A300" s="3">
         <v>41782</v>
       </c>
       <c r="B300">
@@ -2764,7 +2790,7 @@
       </c>
     </row>
     <row r="301" spans="1:2">
-      <c r="A301" s="2">
+      <c r="A301" s="3">
         <v>41789</v>
       </c>
       <c r="B301">
@@ -2772,7 +2798,7 @@
       </c>
     </row>
     <row r="302" spans="1:2">
-      <c r="A302" s="2">
+      <c r="A302" s="3">
         <v>41796</v>
       </c>
       <c r="B302">
@@ -2780,7 +2806,7 @@
       </c>
     </row>
     <row r="303" spans="1:2">
-      <c r="A303" s="2">
+      <c r="A303" s="3">
         <v>41803</v>
       </c>
       <c r="B303">
@@ -2788,7 +2814,7 @@
       </c>
     </row>
     <row r="304" spans="1:2">
-      <c r="A304" s="2">
+      <c r="A304" s="3">
         <v>41810</v>
       </c>
       <c r="B304">
@@ -2796,7 +2822,7 @@
       </c>
     </row>
     <row r="305" spans="1:2">
-      <c r="A305" s="2">
+      <c r="A305" s="3">
         <v>41817</v>
       </c>
       <c r="B305">
@@ -2804,7 +2830,7 @@
       </c>
     </row>
     <row r="306" spans="1:2">
-      <c r="A306" s="2">
+      <c r="A306" s="3">
         <v>41824</v>
       </c>
       <c r="B306">
@@ -2812,7 +2838,7 @@
       </c>
     </row>
     <row r="307" spans="1:2">
-      <c r="A307" s="2">
+      <c r="A307" s="3">
         <v>41831</v>
       </c>
       <c r="B307">
@@ -2820,7 +2846,7 @@
       </c>
     </row>
     <row r="308" spans="1:2">
-      <c r="A308" s="2">
+      <c r="A308" s="3">
         <v>41838</v>
       </c>
       <c r="B308">
@@ -2828,7 +2854,7 @@
       </c>
     </row>
     <row r="309" spans="1:2">
-      <c r="A309" s="2">
+      <c r="A309" s="3">
         <v>41845</v>
       </c>
       <c r="B309">
@@ -2836,7 +2862,7 @@
       </c>
     </row>
     <row r="310" spans="1:2">
-      <c r="A310" s="2">
+      <c r="A310" s="3">
         <v>41852</v>
       </c>
       <c r="B310">
@@ -2844,7 +2870,7 @@
       </c>
     </row>
     <row r="311" spans="1:2">
-      <c r="A311" s="2">
+      <c r="A311" s="3">
         <v>41859</v>
       </c>
       <c r="B311">
@@ -2852,7 +2878,7 @@
       </c>
     </row>
     <row r="312" spans="1:2">
-      <c r="A312" s="2">
+      <c r="A312" s="3">
         <v>41866</v>
       </c>
       <c r="B312">
@@ -2860,7 +2886,7 @@
       </c>
     </row>
     <row r="313" spans="1:2">
-      <c r="A313" s="2">
+      <c r="A313" s="3">
         <v>41873</v>
       </c>
       <c r="B313">
@@ -2868,7 +2894,7 @@
       </c>
     </row>
     <row r="314" spans="1:2">
-      <c r="A314" s="2">
+      <c r="A314" s="3">
         <v>41880</v>
       </c>
       <c r="B314">
@@ -2876,7 +2902,7 @@
       </c>
     </row>
     <row r="315" spans="1:2">
-      <c r="A315" s="2">
+      <c r="A315" s="3">
         <v>41887</v>
       </c>
       <c r="B315">
@@ -2884,7 +2910,7 @@
       </c>
     </row>
     <row r="316" spans="1:2">
-      <c r="A316" s="2">
+      <c r="A316" s="3">
         <v>41894</v>
       </c>
       <c r="B316">
@@ -2892,7 +2918,7 @@
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="2">
+      <c r="A317" s="3">
         <v>41901</v>
       </c>
       <c r="B317">
@@ -2900,7 +2926,7 @@
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="2">
+      <c r="A318" s="3">
         <v>41908</v>
       </c>
       <c r="B318">
@@ -2908,7 +2934,7 @@
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="2">
+      <c r="A319" s="3">
         <v>41915</v>
       </c>
       <c r="B319">
@@ -2916,7 +2942,7 @@
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="2">
+      <c r="A320" s="3">
         <v>41922</v>
       </c>
       <c r="B320">
@@ -2924,7 +2950,7 @@
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="2">
+      <c r="A321" s="3">
         <v>41929</v>
       </c>
       <c r="B321">
@@ -2932,7 +2958,7 @@
       </c>
     </row>
     <row r="322" spans="1:2">
-      <c r="A322" s="2">
+      <c r="A322" s="3">
         <v>41936</v>
       </c>
       <c r="B322">
@@ -2940,7 +2966,7 @@
       </c>
     </row>
     <row r="323" spans="1:2">
-      <c r="A323" s="2">
+      <c r="A323" s="3">
         <v>41943</v>
       </c>
       <c r="B323">
@@ -2948,7 +2974,7 @@
       </c>
     </row>
     <row r="324" spans="1:2">
-      <c r="A324" s="2">
+      <c r="A324" s="3">
         <v>41950</v>
       </c>
       <c r="B324">
@@ -2956,7 +2982,7 @@
       </c>
     </row>
     <row r="325" spans="1:2">
-      <c r="A325" s="2">
+      <c r="A325" s="3">
         <v>41957</v>
       </c>
       <c r="B325">
@@ -2964,7 +2990,7 @@
       </c>
     </row>
     <row r="326" spans="1:2">
-      <c r="A326" s="2">
+      <c r="A326" s="3">
         <v>41964</v>
       </c>
       <c r="B326">
@@ -2972,7 +2998,7 @@
       </c>
     </row>
     <row r="327" spans="1:2">
-      <c r="A327" s="2">
+      <c r="A327" s="3">
         <v>41971</v>
       </c>
       <c r="B327">
@@ -2980,7 +3006,7 @@
       </c>
     </row>
     <row r="328" spans="1:2">
-      <c r="A328" s="2">
+      <c r="A328" s="3">
         <v>41978</v>
       </c>
       <c r="B328">
@@ -2988,7 +3014,7 @@
       </c>
     </row>
     <row r="329" spans="1:2">
-      <c r="A329" s="2">
+      <c r="A329" s="3">
         <v>41985</v>
       </c>
       <c r="B329">
@@ -2996,7 +3022,7 @@
       </c>
     </row>
     <row r="330" spans="1:2">
-      <c r="A330" s="2">
+      <c r="A330" s="3">
         <v>41992</v>
       </c>
       <c r="B330">
@@ -3004,7 +3030,7 @@
       </c>
     </row>
     <row r="331" spans="1:2">
-      <c r="A331" s="2">
+      <c r="A331" s="3">
         <v>41999</v>
       </c>
       <c r="B331">
@@ -3012,7 +3038,7 @@
       </c>
     </row>
     <row r="332" spans="1:2">
-      <c r="A332" s="2">
+      <c r="A332" s="3">
         <v>42006</v>
       </c>
       <c r="B332">
@@ -3020,7 +3046,7 @@
       </c>
     </row>
     <row r="333" spans="1:2">
-      <c r="A333" s="2">
+      <c r="A333" s="3">
         <v>42013</v>
       </c>
       <c r="B333">
@@ -3028,7 +3054,7 @@
       </c>
     </row>
     <row r="334" spans="1:2">
-      <c r="A334" s="2">
+      <c r="A334" s="3">
         <v>42020</v>
       </c>
       <c r="B334">
@@ -3036,7 +3062,7 @@
       </c>
     </row>
     <row r="335" spans="1:2">
-      <c r="A335" s="2">
+      <c r="A335" s="3">
         <v>42027</v>
       </c>
       <c r="B335">
@@ -3044,7 +3070,7 @@
       </c>
     </row>
     <row r="336" spans="1:2">
-      <c r="A336" s="2">
+      <c r="A336" s="3">
         <v>42034</v>
       </c>
       <c r="B336">
@@ -3052,7 +3078,7 @@
       </c>
     </row>
     <row r="337" spans="1:2">
-      <c r="A337" s="2">
+      <c r="A337" s="3">
         <v>42041</v>
       </c>
       <c r="B337">
@@ -3060,7 +3086,7 @@
       </c>
     </row>
     <row r="338" spans="1:2">
-      <c r="A338" s="2">
+      <c r="A338" s="3">
         <v>42048</v>
       </c>
       <c r="B338">
@@ -3068,7 +3094,7 @@
       </c>
     </row>
     <row r="339" spans="1:2">
-      <c r="A339" s="2">
+      <c r="A339" s="3">
         <v>42055</v>
       </c>
       <c r="B339">
@@ -3076,7 +3102,7 @@
       </c>
     </row>
     <row r="340" spans="1:2">
-      <c r="A340" s="2">
+      <c r="A340" s="3">
         <v>42062</v>
       </c>
       <c r="B340">
@@ -3084,7 +3110,7 @@
       </c>
     </row>
     <row r="341" spans="1:2">
-      <c r="A341" s="2">
+      <c r="A341" s="3">
         <v>42069</v>
       </c>
       <c r="B341">
@@ -3092,7 +3118,7 @@
       </c>
     </row>
     <row r="342" spans="1:2">
-      <c r="A342" s="2">
+      <c r="A342" s="3">
         <v>42076</v>
       </c>
       <c r="B342">
@@ -3100,7 +3126,7 @@
       </c>
     </row>
     <row r="343" spans="1:2">
-      <c r="A343" s="2">
+      <c r="A343" s="3">
         <v>42083</v>
       </c>
       <c r="B343">
@@ -3108,7 +3134,7 @@
       </c>
     </row>
     <row r="344" spans="1:2">
-      <c r="A344" s="2">
+      <c r="A344" s="3">
         <v>42090</v>
       </c>
       <c r="B344">
@@ -3116,7 +3142,7 @@
       </c>
     </row>
     <row r="345" spans="1:2">
-      <c r="A345" s="2">
+      <c r="A345" s="3">
         <v>42097</v>
       </c>
       <c r="B345">
@@ -3124,7 +3150,7 @@
       </c>
     </row>
     <row r="346" spans="1:2">
-      <c r="A346" s="2">
+      <c r="A346" s="3">
         <v>42104</v>
       </c>
       <c r="B346">
@@ -3132,7 +3158,7 @@
       </c>
     </row>
     <row r="347" spans="1:2">
-      <c r="A347" s="2">
+      <c r="A347" s="3">
         <v>42111</v>
       </c>
       <c r="B347">
@@ -3140,7 +3166,7 @@
       </c>
     </row>
     <row r="348" spans="1:2">
-      <c r="A348" s="2">
+      <c r="A348" s="3">
         <v>42118</v>
       </c>
       <c r="B348">
@@ -3148,7 +3174,7 @@
       </c>
     </row>
     <row r="349" spans="1:2">
-      <c r="A349" s="2">
+      <c r="A349" s="3">
         <v>42125</v>
       </c>
       <c r="B349">
@@ -3156,7 +3182,7 @@
       </c>
     </row>
     <row r="350" spans="1:2">
-      <c r="A350" s="2">
+      <c r="A350" s="3">
         <v>42132</v>
       </c>
       <c r="B350">
@@ -3164,7 +3190,7 @@
       </c>
     </row>
     <row r="351" spans="1:2">
-      <c r="A351" s="2">
+      <c r="A351" s="3">
         <v>42139</v>
       </c>
       <c r="B351">
@@ -3172,7 +3198,7 @@
       </c>
     </row>
     <row r="352" spans="1:2">
-      <c r="A352" s="2">
+      <c r="A352" s="3">
         <v>42146</v>
       </c>
       <c r="B352">
@@ -3180,7 +3206,7 @@
       </c>
     </row>
     <row r="353" spans="1:2">
-      <c r="A353" s="2">
+      <c r="A353" s="3">
         <v>42153</v>
       </c>
       <c r="B353">
@@ -3188,7 +3214,7 @@
       </c>
     </row>
     <row r="354" spans="1:2">
-      <c r="A354" s="2">
+      <c r="A354" s="3">
         <v>42160</v>
       </c>
       <c r="B354">
@@ -3196,7 +3222,7 @@
       </c>
     </row>
     <row r="355" spans="1:2">
-      <c r="A355" s="2">
+      <c r="A355" s="3">
         <v>42167</v>
       </c>
       <c r="B355">
@@ -3204,7 +3230,7 @@
       </c>
     </row>
     <row r="356" spans="1:2">
-      <c r="A356" s="2">
+      <c r="A356" s="3">
         <v>42174</v>
       </c>
       <c r="B356">
@@ -3212,7 +3238,7 @@
       </c>
     </row>
     <row r="357" spans="1:2">
-      <c r="A357" s="2">
+      <c r="A357" s="3">
         <v>42181</v>
       </c>
       <c r="B357">
@@ -3220,7 +3246,7 @@
       </c>
     </row>
     <row r="358" spans="1:2">
-      <c r="A358" s="2">
+      <c r="A358" s="3">
         <v>42188</v>
       </c>
       <c r="B358">
@@ -3228,7 +3254,7 @@
       </c>
     </row>
     <row r="359" spans="1:2">
-      <c r="A359" s="2">
+      <c r="A359" s="3">
         <v>42195</v>
       </c>
       <c r="B359">
@@ -3236,7 +3262,7 @@
       </c>
     </row>
     <row r="360" spans="1:2">
-      <c r="A360" s="2">
+      <c r="A360" s="3">
         <v>42202</v>
       </c>
       <c r="B360">
@@ -3244,7 +3270,7 @@
       </c>
     </row>
     <row r="361" spans="1:2">
-      <c r="A361" s="2">
+      <c r="A361" s="3">
         <v>42209</v>
       </c>
       <c r="B361">
@@ -3252,7 +3278,7 @@
       </c>
     </row>
     <row r="362" spans="1:2">
-      <c r="A362" s="2">
+      <c r="A362" s="3">
         <v>42216</v>
       </c>
       <c r="B362">
@@ -3260,7 +3286,7 @@
       </c>
     </row>
     <row r="363" spans="1:2">
-      <c r="A363" s="2">
+      <c r="A363" s="3">
         <v>42223</v>
       </c>
       <c r="B363">
@@ -3268,7 +3294,7 @@
       </c>
     </row>
     <row r="364" spans="1:2">
-      <c r="A364" s="2">
+      <c r="A364" s="3">
         <v>42230</v>
       </c>
       <c r="B364">
@@ -3276,7 +3302,7 @@
       </c>
     </row>
     <row r="365" spans="1:2">
-      <c r="A365" s="2">
+      <c r="A365" s="3">
         <v>42237</v>
       </c>
       <c r="B365">
@@ -3284,7 +3310,7 @@
       </c>
     </row>
     <row r="366" spans="1:2">
-      <c r="A366" s="2">
+      <c r="A366" s="3">
         <v>42244</v>
       </c>
       <c r="B366">
@@ -3292,7 +3318,7 @@
       </c>
     </row>
     <row r="367" spans="1:2">
-      <c r="A367" s="2">
+      <c r="A367" s="3">
         <v>42251</v>
       </c>
       <c r="B367">
@@ -3300,7 +3326,7 @@
       </c>
     </row>
     <row r="368" spans="1:2">
-      <c r="A368" s="2">
+      <c r="A368" s="3">
         <v>42258</v>
       </c>
       <c r="B368">
@@ -3308,7 +3334,7 @@
       </c>
     </row>
     <row r="369" spans="1:2">
-      <c r="A369" s="2">
+      <c r="A369" s="3">
         <v>42265</v>
       </c>
       <c r="B369">
@@ -3316,7 +3342,7 @@
       </c>
     </row>
     <row r="370" spans="1:2">
-      <c r="A370" s="2">
+      <c r="A370" s="3">
         <v>42272</v>
       </c>
       <c r="B370">
@@ -3324,7 +3350,7 @@
       </c>
     </row>
     <row r="371" spans="1:2">
-      <c r="A371" s="2">
+      <c r="A371" s="3">
         <v>42279</v>
       </c>
       <c r="B371">
@@ -3332,7 +3358,7 @@
       </c>
     </row>
     <row r="372" spans="1:2">
-      <c r="A372" s="2">
+      <c r="A372" s="3">
         <v>42286</v>
       </c>
       <c r="B372">
@@ -3340,7 +3366,7 @@
       </c>
     </row>
     <row r="373" spans="1:2">
-      <c r="A373" s="2">
+      <c r="A373" s="3">
         <v>42293</v>
       </c>
       <c r="B373">
@@ -3348,7 +3374,7 @@
       </c>
     </row>
     <row r="374" spans="1:2">
-      <c r="A374" s="2">
+      <c r="A374" s="3">
         <v>42300</v>
       </c>
       <c r="B374">
@@ -3356,7 +3382,7 @@
       </c>
     </row>
     <row r="375" spans="1:2">
-      <c r="A375" s="2">
+      <c r="A375" s="3">
         <v>42307</v>
       </c>
       <c r="B375">
@@ -3364,7 +3390,7 @@
       </c>
     </row>
     <row r="376" spans="1:2">
-      <c r="A376" s="2">
+      <c r="A376" s="3">
         <v>42314</v>
       </c>
       <c r="B376">
@@ -3372,7 +3398,7 @@
       </c>
     </row>
     <row r="377" spans="1:2">
-      <c r="A377" s="2">
+      <c r="A377" s="3">
         <v>42321</v>
       </c>
       <c r="B377">
@@ -3380,7 +3406,7 @@
       </c>
     </row>
     <row r="378" spans="1:2">
-      <c r="A378" s="2">
+      <c r="A378" s="3">
         <v>42328</v>
       </c>
       <c r="B378">
@@ -3388,7 +3414,7 @@
       </c>
     </row>
     <row r="379" spans="1:2">
-      <c r="A379" s="2">
+      <c r="A379" s="3">
         <v>42335</v>
       </c>
       <c r="B379">
@@ -3396,7 +3422,7 @@
       </c>
     </row>
     <row r="380" spans="1:2">
-      <c r="A380" s="2">
+      <c r="A380" s="3">
         <v>42342</v>
       </c>
       <c r="B380">
@@ -3404,7 +3430,7 @@
       </c>
     </row>
     <row r="381" spans="1:2">
-      <c r="A381" s="2">
+      <c r="A381" s="3">
         <v>42349</v>
       </c>
       <c r="B381">
@@ -3412,7 +3438,7 @@
       </c>
     </row>
     <row r="382" spans="1:2">
-      <c r="A382" s="2">
+      <c r="A382" s="3">
         <v>42356</v>
       </c>
       <c r="B382">
@@ -3420,7 +3446,7 @@
       </c>
     </row>
     <row r="383" spans="1:2">
-      <c r="A383" s="2">
+      <c r="A383" s="3">
         <v>42363</v>
       </c>
       <c r="B383">
@@ -3428,7 +3454,7 @@
       </c>
     </row>
     <row r="384" spans="1:2">
-      <c r="A384" s="2">
+      <c r="A384" s="3">
         <v>42370</v>
       </c>
       <c r="B384">
@@ -3436,7 +3462,7 @@
       </c>
     </row>
     <row r="385" spans="1:2">
-      <c r="A385" s="2">
+      <c r="A385" s="3">
         <v>42377</v>
       </c>
       <c r="B385">
@@ -3444,7 +3470,7 @@
       </c>
     </row>
     <row r="386" spans="1:2">
-      <c r="A386" s="2">
+      <c r="A386" s="3">
         <v>42384</v>
       </c>
       <c r="B386">
@@ -3452,7 +3478,7 @@
       </c>
     </row>
     <row r="387" spans="1:2">
-      <c r="A387" s="2">
+      <c r="A387" s="3">
         <v>42391</v>
       </c>
       <c r="B387">
@@ -3460,7 +3486,7 @@
       </c>
     </row>
     <row r="388" spans="1:2">
-      <c r="A388" s="2">
+      <c r="A388" s="3">
         <v>42398</v>
       </c>
       <c r="B388">
@@ -3468,7 +3494,7 @@
       </c>
     </row>
     <row r="389" spans="1:2">
-      <c r="A389" s="2">
+      <c r="A389" s="3">
         <v>42405</v>
       </c>
       <c r="B389">
@@ -3476,7 +3502,7 @@
       </c>
     </row>
     <row r="390" spans="1:2">
-      <c r="A390" s="2">
+      <c r="A390" s="3">
         <v>42412</v>
       </c>
       <c r="B390">
@@ -3484,7 +3510,7 @@
       </c>
     </row>
     <row r="391" spans="1:2">
-      <c r="A391" s="2">
+      <c r="A391" s="3">
         <v>42419</v>
       </c>
       <c r="B391">
@@ -3492,7 +3518,7 @@
       </c>
     </row>
     <row r="392" spans="1:2">
-      <c r="A392" s="2">
+      <c r="A392" s="3">
         <v>42426</v>
       </c>
       <c r="B392">
@@ -3500,7 +3526,7 @@
       </c>
     </row>
     <row r="393" spans="1:2">
-      <c r="A393" s="2">
+      <c r="A393" s="3">
         <v>42433</v>
       </c>
       <c r="B393">
@@ -3508,7 +3534,7 @@
       </c>
     </row>
     <row r="394" spans="1:2">
-      <c r="A394" s="2">
+      <c r="A394" s="3">
         <v>42440</v>
       </c>
       <c r="B394">
@@ -3516,7 +3542,7 @@
       </c>
     </row>
     <row r="395" spans="1:2">
-      <c r="A395" s="2">
+      <c r="A395" s="3">
         <v>42447</v>
       </c>
       <c r="B395">
@@ -3524,7 +3550,7 @@
       </c>
     </row>
     <row r="396" spans="1:2">
-      <c r="A396" s="2">
+      <c r="A396" s="3">
         <v>42454</v>
       </c>
       <c r="B396">
@@ -3532,7 +3558,7 @@
       </c>
     </row>
     <row r="397" spans="1:2">
-      <c r="A397" s="2">
+      <c r="A397" s="3">
         <v>42461</v>
       </c>
       <c r="B397">
@@ -3540,7 +3566,7 @@
       </c>
     </row>
     <row r="398" spans="1:2">
-      <c r="A398" s="2">
+      <c r="A398" s="3">
         <v>42468</v>
       </c>
       <c r="B398">
@@ -3548,7 +3574,7 @@
       </c>
     </row>
     <row r="399" spans="1:2">
-      <c r="A399" s="2">
+      <c r="A399" s="3">
         <v>42475</v>
       </c>
       <c r="B399">
@@ -3556,7 +3582,7 @@
       </c>
     </row>
     <row r="400" spans="1:2">
-      <c r="A400" s="2">
+      <c r="A400" s="3">
         <v>42482</v>
       </c>
       <c r="B400">
@@ -3564,7 +3590,7 @@
       </c>
     </row>
     <row r="401" spans="1:2">
-      <c r="A401" s="2">
+      <c r="A401" s="3">
         <v>42489</v>
       </c>
       <c r="B401">
@@ -3572,7 +3598,7 @@
       </c>
     </row>
     <row r="402" spans="1:2">
-      <c r="A402" s="2">
+      <c r="A402" s="3">
         <v>42496</v>
       </c>
       <c r="B402">
@@ -3580,7 +3606,7 @@
       </c>
     </row>
     <row r="403" spans="1:2">
-      <c r="A403" s="2">
+      <c r="A403" s="3">
         <v>42503</v>
       </c>
       <c r="B403">
@@ -3588,7 +3614,7 @@
       </c>
     </row>
     <row r="404" spans="1:2">
-      <c r="A404" s="2">
+      <c r="A404" s="3">
         <v>42510</v>
       </c>
       <c r="B404">
@@ -3596,7 +3622,7 @@
       </c>
     </row>
     <row r="405" spans="1:2">
-      <c r="A405" s="2">
+      <c r="A405" s="3">
         <v>42517</v>
       </c>
       <c r="B405">
@@ -3604,7 +3630,7 @@
       </c>
     </row>
     <row r="406" spans="1:2">
-      <c r="A406" s="2">
+      <c r="A406" s="3">
         <v>42524</v>
       </c>
       <c r="B406">
@@ -3612,7 +3638,7 @@
       </c>
     </row>
     <row r="407" spans="1:2">
-      <c r="A407" s="2">
+      <c r="A407" s="3">
         <v>42531</v>
       </c>
       <c r="B407">
@@ -3620,7 +3646,7 @@
       </c>
     </row>
     <row r="408" spans="1:2">
-      <c r="A408" s="2">
+      <c r="A408" s="3">
         <v>42538</v>
       </c>
       <c r="B408">
@@ -3628,7 +3654,7 @@
       </c>
     </row>
     <row r="409" spans="1:2">
-      <c r="A409" s="2">
+      <c r="A409" s="3">
         <v>42545</v>
       </c>
       <c r="B409">
@@ -3636,7 +3662,7 @@
       </c>
     </row>
     <row r="410" spans="1:2">
-      <c r="A410" s="2">
+      <c r="A410" s="3">
         <v>42552</v>
       </c>
       <c r="B410">
@@ -3644,7 +3670,7 @@
       </c>
     </row>
     <row r="411" spans="1:2">
-      <c r="A411" s="2">
+      <c r="A411" s="3">
         <v>42559</v>
       </c>
       <c r="B411">
@@ -3652,7 +3678,7 @@
       </c>
     </row>
     <row r="412" spans="1:2">
-      <c r="A412" s="2">
+      <c r="A412" s="3">
         <v>42566</v>
       </c>
       <c r="B412">
@@ -3660,7 +3686,7 @@
       </c>
     </row>
     <row r="413" spans="1:2">
-      <c r="A413" s="2">
+      <c r="A413" s="3">
         <v>42573</v>
       </c>
       <c r="B413">
@@ -3668,7 +3694,7 @@
       </c>
     </row>
     <row r="414" spans="1:2">
-      <c r="A414" s="2">
+      <c r="A414" s="3">
         <v>42580</v>
       </c>
       <c r="B414">
@@ -3676,7 +3702,7 @@
       </c>
     </row>
     <row r="415" spans="1:2">
-      <c r="A415" s="2">
+      <c r="A415" s="3">
         <v>42587</v>
       </c>
       <c r="B415">
@@ -3684,7 +3710,7 @@
       </c>
     </row>
     <row r="416" spans="1:2">
-      <c r="A416" s="2">
+      <c r="A416" s="3">
         <v>42594</v>
       </c>
       <c r="B416">
@@ -3692,7 +3718,7 @@
       </c>
     </row>
     <row r="417" spans="1:2">
-      <c r="A417" s="2">
+      <c r="A417" s="3">
         <v>42601</v>
       </c>
       <c r="B417">
@@ -3700,7 +3726,7 @@
       </c>
     </row>
     <row r="418" spans="1:2">
-      <c r="A418" s="2">
+      <c r="A418" s="3">
         <v>42608</v>
       </c>
       <c r="B418">
@@ -3708,7 +3734,7 @@
       </c>
     </row>
     <row r="419" spans="1:2">
-      <c r="A419" s="2">
+      <c r="A419" s="3">
         <v>42615</v>
       </c>
       <c r="B419">
@@ -3716,7 +3742,7 @@
       </c>
     </row>
     <row r="420" spans="1:2">
-      <c r="A420" s="2">
+      <c r="A420" s="3">
         <v>42622</v>
       </c>
       <c r="B420">
@@ -3724,7 +3750,7 @@
       </c>
     </row>
     <row r="421" spans="1:2">
-      <c r="A421" s="2">
+      <c r="A421" s="3">
         <v>42629</v>
       </c>
       <c r="B421">
@@ -3732,7 +3758,7 @@
       </c>
     </row>
     <row r="422" spans="1:2">
-      <c r="A422" s="2">
+      <c r="A422" s="3">
         <v>42636</v>
       </c>
       <c r="B422">
@@ -3740,7 +3766,7 @@
       </c>
     </row>
     <row r="423" spans="1:2">
-      <c r="A423" s="2">
+      <c r="A423" s="3">
         <v>42643</v>
       </c>
       <c r="B423">
@@ -3748,7 +3774,7 @@
       </c>
     </row>
     <row r="424" spans="1:2">
-      <c r="A424" s="2">
+      <c r="A424" s="3">
         <v>42650</v>
       </c>
       <c r="B424">
@@ -3756,7 +3782,7 @@
       </c>
     </row>
     <row r="425" spans="1:2">
-      <c r="A425" s="2">
+      <c r="A425" s="3">
         <v>42657</v>
       </c>
       <c r="B425">
@@ -3764,7 +3790,7 @@
       </c>
     </row>
     <row r="426" spans="1:2">
-      <c r="A426" s="2">
+      <c r="A426" s="3">
         <v>42664</v>
       </c>
       <c r="B426">
@@ -3772,7 +3798,7 @@
       </c>
     </row>
     <row r="427" spans="1:2">
-      <c r="A427" s="2">
+      <c r="A427" s="3">
         <v>42671</v>
       </c>
       <c r="B427">
@@ -3780,7 +3806,7 @@
       </c>
     </row>
     <row r="428" spans="1:2">
-      <c r="A428" s="2">
+      <c r="A428" s="3">
         <v>42678</v>
       </c>
       <c r="B428">
@@ -3788,7 +3814,7 @@
       </c>
     </row>
     <row r="429" spans="1:2">
-      <c r="A429" s="2">
+      <c r="A429" s="3">
         <v>42685</v>
       </c>
       <c r="B429">
@@ -3796,7 +3822,7 @@
       </c>
     </row>
     <row r="430" spans="1:2">
-      <c r="A430" s="2">
+      <c r="A430" s="3">
         <v>42692</v>
       </c>
       <c r="B430">
@@ -3804,7 +3830,7 @@
       </c>
     </row>
     <row r="431" spans="1:2">
-      <c r="A431" s="2">
+      <c r="A431" s="3">
         <v>42699</v>
       </c>
       <c r="B431">
@@ -3812,7 +3838,7 @@
       </c>
     </row>
     <row r="432" spans="1:2">
-      <c r="A432" s="2">
+      <c r="A432" s="3">
         <v>42706</v>
       </c>
       <c r="B432">
@@ -3820,7 +3846,7 @@
       </c>
     </row>
     <row r="433" spans="1:2">
-      <c r="A433" s="2">
+      <c r="A433" s="3">
         <v>42713</v>
       </c>
       <c r="B433">
@@ -3828,7 +3854,7 @@
       </c>
     </row>
     <row r="434" spans="1:2">
-      <c r="A434" s="2">
+      <c r="A434" s="3">
         <v>42720</v>
       </c>
       <c r="B434">
@@ -3836,7 +3862,7 @@
       </c>
     </row>
     <row r="435" spans="1:2">
-      <c r="A435" s="2">
+      <c r="A435" s="3">
         <v>42727</v>
       </c>
       <c r="B435">
@@ -3844,7 +3870,7 @@
       </c>
     </row>
     <row r="436" spans="1:2">
-      <c r="A436" s="2">
+      <c r="A436" s="3">
         <v>42734</v>
       </c>
       <c r="B436">
@@ -3852,7 +3878,7 @@
       </c>
     </row>
     <row r="437" spans="1:2">
-      <c r="A437" s="2">
+      <c r="A437" s="3">
         <v>42741</v>
       </c>
       <c r="B437">
@@ -3860,7 +3886,7 @@
       </c>
     </row>
     <row r="438" spans="1:2">
-      <c r="A438" s="2">
+      <c r="A438" s="3">
         <v>42748</v>
       </c>
       <c r="B438">
@@ -3868,7 +3894,7 @@
       </c>
     </row>
     <row r="439" spans="1:2">
-      <c r="A439" s="2">
+      <c r="A439" s="3">
         <v>42755</v>
       </c>
       <c r="B439">
@@ -3876,7 +3902,7 @@
       </c>
     </row>
     <row r="440" spans="1:2">
-      <c r="A440" s="2">
+      <c r="A440" s="3">
         <v>42762</v>
       </c>
       <c r="B440">
@@ -3884,7 +3910,7 @@
       </c>
     </row>
     <row r="441" spans="1:2">
-      <c r="A441" s="2">
+      <c r="A441" s="3">
         <v>42769</v>
       </c>
       <c r="B441">
@@ -3892,7 +3918,7 @@
       </c>
     </row>
     <row r="442" spans="1:2">
-      <c r="A442" s="2">
+      <c r="A442" s="3">
         <v>42776</v>
       </c>
       <c r="B442">
@@ -3900,7 +3926,7 @@
       </c>
     </row>
     <row r="443" spans="1:2">
-      <c r="A443" s="2">
+      <c r="A443" s="3">
         <v>42783</v>
       </c>
       <c r="B443">
@@ -3908,7 +3934,7 @@
       </c>
     </row>
     <row r="444" spans="1:2">
-      <c r="A444" s="2">
+      <c r="A444" s="3">
         <v>42790</v>
       </c>
       <c r="B444">
@@ -3916,7 +3942,7 @@
       </c>
     </row>
     <row r="445" spans="1:2">
-      <c r="A445" s="2">
+      <c r="A445" s="3">
         <v>42797</v>
       </c>
       <c r="B445">
@@ -3924,7 +3950,7 @@
       </c>
     </row>
     <row r="446" spans="1:2">
-      <c r="A446" s="2">
+      <c r="A446" s="3">
         <v>42804</v>
       </c>
       <c r="B446">
@@ -3932,7 +3958,7 @@
       </c>
     </row>
     <row r="447" spans="1:2">
-      <c r="A447" s="2">
+      <c r="A447" s="3">
         <v>42811</v>
       </c>
       <c r="B447">
@@ -3940,7 +3966,7 @@
       </c>
     </row>
     <row r="448" spans="1:2">
-      <c r="A448" s="2">
+      <c r="A448" s="3">
         <v>42818</v>
       </c>
       <c r="B448">
@@ -3948,7 +3974,7 @@
       </c>
     </row>
     <row r="449" spans="1:2">
-      <c r="A449" s="2">
+      <c r="A449" s="3">
         <v>42825</v>
       </c>
       <c r="B449">
@@ -3956,7 +3982,7 @@
       </c>
     </row>
     <row r="450" spans="1:2">
-      <c r="A450" s="2">
+      <c r="A450" s="3">
         <v>42832</v>
       </c>
       <c r="B450">
@@ -3964,7 +3990,7 @@
       </c>
     </row>
     <row r="451" spans="1:2">
-      <c r="A451" s="2">
+      <c r="A451" s="3">
         <v>42839</v>
       </c>
       <c r="B451">
@@ -3972,7 +3998,7 @@
       </c>
     </row>
     <row r="452" spans="1:2">
-      <c r="A452" s="2">
+      <c r="A452" s="3">
         <v>42846</v>
       </c>
       <c r="B452">
@@ -3980,7 +4006,7 @@
       </c>
     </row>
     <row r="453" spans="1:2">
-      <c r="A453" s="2">
+      <c r="A453" s="3">
         <v>42853</v>
       </c>
       <c r="B453">
@@ -3988,7 +4014,7 @@
       </c>
     </row>
     <row r="454" spans="1:2">
-      <c r="A454" s="2">
+      <c r="A454" s="3">
         <v>42860</v>
       </c>
       <c r="B454">
@@ -3996,7 +4022,7 @@
       </c>
     </row>
     <row r="455" spans="1:2">
-      <c r="A455" s="2">
+      <c r="A455" s="3">
         <v>42867</v>
       </c>
       <c r="B455">
@@ -4004,7 +4030,7 @@
       </c>
     </row>
     <row r="456" spans="1:2">
-      <c r="A456" s="2">
+      <c r="A456" s="3">
         <v>42874</v>
       </c>
       <c r="B456">
@@ -4012,7 +4038,7 @@
       </c>
     </row>
     <row r="457" spans="1:2">
-      <c r="A457" s="2">
+      <c r="A457" s="3">
         <v>42881</v>
       </c>
       <c r="B457">
@@ -4020,7 +4046,7 @@
       </c>
     </row>
     <row r="458" spans="1:2">
-      <c r="A458" s="2">
+      <c r="A458" s="3">
         <v>42888</v>
       </c>
       <c r="B458">
@@ -4028,7 +4054,7 @@
       </c>
     </row>
     <row r="459" spans="1:2">
-      <c r="A459" s="2">
+      <c r="A459" s="3">
         <v>42895</v>
       </c>
       <c r="B459">
@@ -4036,7 +4062,7 @@
       </c>
     </row>
     <row r="460" spans="1:2">
-      <c r="A460" s="2">
+      <c r="A460" s="3">
         <v>42902</v>
       </c>
       <c r="B460">
@@ -4044,7 +4070,7 @@
       </c>
     </row>
     <row r="461" spans="1:2">
-      <c r="A461" s="2">
+      <c r="A461" s="3">
         <v>42909</v>
       </c>
       <c r="B461">
@@ -4052,7 +4078,7 @@
       </c>
     </row>
     <row r="462" spans="1:2">
-      <c r="A462" s="2">
+      <c r="A462" s="3">
         <v>42916</v>
       </c>
       <c r="B462">
@@ -4060,7 +4086,7 @@
       </c>
     </row>
     <row r="463" spans="1:2">
-      <c r="A463" s="2">
+      <c r="A463" s="3">
         <v>42923</v>
       </c>
       <c r="B463">
@@ -4068,7 +4094,7 @@
       </c>
     </row>
     <row r="464" spans="1:2">
-      <c r="A464" s="2">
+      <c r="A464" s="3">
         <v>42930</v>
       </c>
       <c r="B464">
@@ -4076,7 +4102,7 @@
       </c>
     </row>
     <row r="465" spans="1:2">
-      <c r="A465" s="2">
+      <c r="A465" s="3">
         <v>42937</v>
       </c>
       <c r="B465">
@@ -4084,7 +4110,7 @@
       </c>
     </row>
     <row r="466" spans="1:2">
-      <c r="A466" s="2">
+      <c r="A466" s="3">
         <v>42944</v>
       </c>
       <c r="B466">
@@ -4092,7 +4118,7 @@
       </c>
     </row>
     <row r="467" spans="1:2">
-      <c r="A467" s="2">
+      <c r="A467" s="3">
         <v>42951</v>
       </c>
       <c r="B467">
@@ -4100,7 +4126,7 @@
       </c>
     </row>
     <row r="468" spans="1:2">
-      <c r="A468" s="2">
+      <c r="A468" s="3">
         <v>42958</v>
       </c>
       <c r="B468">
@@ -4108,7 +4134,7 @@
       </c>
     </row>
     <row r="469" spans="1:2">
-      <c r="A469" s="2">
+      <c r="A469" s="3">
         <v>42965</v>
       </c>
       <c r="B469">
@@ -4116,7 +4142,7 @@
       </c>
     </row>
     <row r="470" spans="1:2">
-      <c r="A470" s="2">
+      <c r="A470" s="3">
         <v>42972</v>
       </c>
       <c r="B470">
@@ -4124,7 +4150,7 @@
       </c>
     </row>
     <row r="471" spans="1:2">
-      <c r="A471" s="2">
+      <c r="A471" s="3">
         <v>42979</v>
       </c>
       <c r="B471">
@@ -4132,7 +4158,7 @@
       </c>
     </row>
     <row r="472" spans="1:2">
-      <c r="A472" s="2">
+      <c r="A472" s="3">
         <v>42986</v>
       </c>
       <c r="B472">
@@ -4140,7 +4166,7 @@
       </c>
     </row>
     <row r="473" spans="1:2">
-      <c r="A473" s="2">
+      <c r="A473" s="3">
         <v>42993</v>
       </c>
       <c r="B473">
@@ -4148,7 +4174,7 @@
       </c>
     </row>
     <row r="474" spans="1:2">
-      <c r="A474" s="2">
+      <c r="A474" s="3">
         <v>43000</v>
       </c>
       <c r="B474">
@@ -4156,7 +4182,7 @@
       </c>
     </row>
     <row r="475" spans="1:2">
-      <c r="A475" s="2">
+      <c r="A475" s="3">
         <v>43007</v>
       </c>
       <c r="B475">
@@ -4164,7 +4190,7 @@
       </c>
     </row>
     <row r="476" spans="1:2">
-      <c r="A476" s="2">
+      <c r="A476" s="3">
         <v>43014</v>
       </c>
       <c r="B476">
@@ -4172,7 +4198,7 @@
       </c>
     </row>
     <row r="477" spans="1:2">
-      <c r="A477" s="2">
+      <c r="A477" s="3">
         <v>43021</v>
       </c>
       <c r="B477">
@@ -4180,7 +4206,7 @@
       </c>
     </row>
     <row r="478" spans="1:2">
-      <c r="A478" s="2">
+      <c r="A478" s="3">
         <v>43028</v>
       </c>
       <c r="B478">
@@ -4188,7 +4214,7 @@
       </c>
     </row>
     <row r="479" spans="1:2">
-      <c r="A479" s="2">
+      <c r="A479" s="3">
         <v>43035</v>
       </c>
       <c r="B479">
@@ -4196,7 +4222,7 @@
       </c>
     </row>
     <row r="480" spans="1:2">
-      <c r="A480" s="2">
+      <c r="A480" s="3">
         <v>43042</v>
       </c>
       <c r="B480">
@@ -4204,7 +4230,7 @@
       </c>
     </row>
     <row r="481" spans="1:2">
-      <c r="A481" s="2">
+      <c r="A481" s="3">
         <v>43049</v>
       </c>
       <c r="B481">
@@ -4212,7 +4238,7 @@
       </c>
     </row>
     <row r="482" spans="1:2">
-      <c r="A482" s="2">
+      <c r="A482" s="3">
         <v>43056</v>
       </c>
       <c r="B482">
@@ -4220,7 +4246,7 @@
       </c>
     </row>
     <row r="483" spans="1:2">
-      <c r="A483" s="2">
+      <c r="A483" s="3">
         <v>43063</v>
       </c>
       <c r="B483">
@@ -4228,7 +4254,7 @@
       </c>
     </row>
     <row r="484" spans="1:2">
-      <c r="A484" s="2">
+      <c r="A484" s="3">
         <v>43070</v>
       </c>
       <c r="B484">
@@ -4236,7 +4262,7 @@
       </c>
     </row>
     <row r="485" spans="1:2">
-      <c r="A485" s="2">
+      <c r="A485" s="3">
         <v>43077</v>
       </c>
       <c r="B485">
@@ -4244,7 +4270,7 @@
       </c>
     </row>
     <row r="486" spans="1:2">
-      <c r="A486" s="2">
+      <c r="A486" s="3">
         <v>43084</v>
       </c>
       <c r="B486">
@@ -4252,7 +4278,7 @@
       </c>
     </row>
     <row r="487" spans="1:2">
-      <c r="A487" s="2">
+      <c r="A487" s="3">
         <v>43091</v>
       </c>
       <c r="B487">
@@ -4260,7 +4286,7 @@
       </c>
     </row>
     <row r="488" spans="1:2">
-      <c r="A488" s="2">
+      <c r="A488" s="3">
         <v>43098</v>
       </c>
       <c r="B488">
@@ -4268,7 +4294,7 @@
       </c>
     </row>
     <row r="489" spans="1:2">
-      <c r="A489" s="2">
+      <c r="A489" s="3">
         <v>43105</v>
       </c>
       <c r="B489">
@@ -4276,7 +4302,7 @@
       </c>
     </row>
     <row r="490" spans="1:2">
-      <c r="A490" s="2">
+      <c r="A490" s="3">
         <v>43112</v>
       </c>
       <c r="B490">
@@ -4284,7 +4310,7 @@
       </c>
     </row>
     <row r="491" spans="1:2">
-      <c r="A491" s="2">
+      <c r="A491" s="3">
         <v>43119</v>
       </c>
       <c r="B491">
@@ -4292,7 +4318,7 @@
       </c>
     </row>
     <row r="492" spans="1:2">
-      <c r="A492" s="2">
+      <c r="A492" s="3">
         <v>43126</v>
       </c>
       <c r="B492">
@@ -4300,7 +4326,7 @@
       </c>
     </row>
     <row r="493" spans="1:2">
-      <c r="A493" s="2">
+      <c r="A493" s="3">
         <v>43133</v>
       </c>
       <c r="B493">
@@ -4308,7 +4334,7 @@
       </c>
     </row>
     <row r="494" spans="1:2">
-      <c r="A494" s="2">
+      <c r="A494" s="3">
         <v>43140</v>
       </c>
       <c r="B494">
@@ -4316,7 +4342,7 @@
       </c>
     </row>
     <row r="495" spans="1:2">
-      <c r="A495" s="2">
+      <c r="A495" s="3">
         <v>43147</v>
       </c>
       <c r="B495">
@@ -4324,7 +4350,7 @@
       </c>
     </row>
     <row r="496" spans="1:2">
-      <c r="A496" s="2">
+      <c r="A496" s="3">
         <v>43154</v>
       </c>
       <c r="B496">
@@ -4332,7 +4358,7 @@
       </c>
     </row>
     <row r="497" spans="1:2">
-      <c r="A497" s="2">
+      <c r="A497" s="3">
         <v>43161</v>
       </c>
       <c r="B497">
@@ -4340,7 +4366,7 @@
       </c>
     </row>
     <row r="498" spans="1:2">
-      <c r="A498" s="2">
+      <c r="A498" s="3">
         <v>43168</v>
       </c>
       <c r="B498">
@@ -4348,7 +4374,7 @@
       </c>
     </row>
     <row r="499" spans="1:2">
-      <c r="A499" s="2">
+      <c r="A499" s="3">
         <v>43175</v>
       </c>
       <c r="B499">
@@ -4356,7 +4382,7 @@
       </c>
     </row>
     <row r="500" spans="1:2">
-      <c r="A500" s="2">
+      <c r="A500" s="3">
         <v>43182</v>
       </c>
       <c r="B500">
@@ -4364,7 +4390,7 @@
       </c>
     </row>
     <row r="501" spans="1:2">
-      <c r="A501" s="2">
+      <c r="A501" s="3">
         <v>43189</v>
       </c>
       <c r="B501">
@@ -4372,7 +4398,7 @@
       </c>
     </row>
     <row r="502" spans="1:2">
-      <c r="A502" s="2">
+      <c r="A502" s="3">
         <v>43196</v>
       </c>
       <c r="B502">
@@ -4380,7 +4406,7 @@
       </c>
     </row>
     <row r="503" spans="1:2">
-      <c r="A503" s="2">
+      <c r="A503" s="3">
         <v>43203</v>
       </c>
       <c r="B503">
@@ -4388,7 +4414,7 @@
       </c>
     </row>
     <row r="504" spans="1:2">
-      <c r="A504" s="2">
+      <c r="A504" s="3">
         <v>43210</v>
       </c>
       <c r="B504">
@@ -4396,7 +4422,7 @@
       </c>
     </row>
     <row r="505" spans="1:2">
-      <c r="A505" s="2">
+      <c r="A505" s="3">
         <v>43217</v>
       </c>
       <c r="B505">
@@ -4404,7 +4430,7 @@
       </c>
     </row>
     <row r="506" spans="1:2">
-      <c r="A506" s="2">
+      <c r="A506" s="3">
         <v>43224</v>
       </c>
       <c r="B506">
@@ -4412,7 +4438,7 @@
       </c>
     </row>
     <row r="507" spans="1:2">
-      <c r="A507" s="2">
+      <c r="A507" s="3">
         <v>43231</v>
       </c>
       <c r="B507">
@@ -4420,7 +4446,7 @@
       </c>
     </row>
     <row r="508" spans="1:2">
-      <c r="A508" s="2">
+      <c r="A508" s="3">
         <v>43238</v>
       </c>
       <c r="B508">
@@ -4428,7 +4454,7 @@
       </c>
     </row>
     <row r="509" spans="1:2">
-      <c r="A509" s="2">
+      <c r="A509" s="3">
         <v>43245</v>
       </c>
       <c r="B509">
@@ -4436,7 +4462,7 @@
       </c>
     </row>
     <row r="510" spans="1:2">
-      <c r="A510" s="2">
+      <c r="A510" s="3">
         <v>43252</v>
       </c>
       <c r="B510">
@@ -4444,7 +4470,7 @@
       </c>
     </row>
     <row r="511" spans="1:2">
-      <c r="A511" s="2">
+      <c r="A511" s="3">
         <v>43259</v>
       </c>
       <c r="B511">
@@ -4452,7 +4478,7 @@
       </c>
     </row>
     <row r="512" spans="1:2">
-      <c r="A512" s="2">
+      <c r="A512" s="3">
         <v>43266</v>
       </c>
       <c r="B512">
@@ -4460,7 +4486,7 @@
       </c>
     </row>
     <row r="513" spans="1:2">
-      <c r="A513" s="2">
+      <c r="A513" s="3">
         <v>43273</v>
       </c>
       <c r="B513">
@@ -4468,7 +4494,7 @@
       </c>
     </row>
     <row r="514" spans="1:2">
-      <c r="A514" s="2">
+      <c r="A514" s="3">
         <v>43280</v>
       </c>
       <c r="B514">
@@ -4476,7 +4502,7 @@
       </c>
     </row>
     <row r="515" spans="1:2">
-      <c r="A515" s="2">
+      <c r="A515" s="3">
         <v>43287</v>
       </c>
       <c r="B515">
@@ -4484,7 +4510,7 @@
       </c>
     </row>
     <row r="516" spans="1:2">
-      <c r="A516" s="2">
+      <c r="A516" s="3">
         <v>43294</v>
       </c>
       <c r="B516">
@@ -4492,7 +4518,7 @@
       </c>
     </row>
     <row r="517" spans="1:2">
-      <c r="A517" s="2">
+      <c r="A517" s="3">
         <v>43301</v>
       </c>
       <c r="B517">
@@ -4500,7 +4526,7 @@
       </c>
     </row>
     <row r="518" spans="1:2">
-      <c r="A518" s="2">
+      <c r="A518" s="3">
         <v>43308</v>
       </c>
       <c r="B518">
@@ -4508,7 +4534,7 @@
       </c>
     </row>
     <row r="519" spans="1:2">
-      <c r="A519" s="2">
+      <c r="A519" s="3">
         <v>43315</v>
       </c>
       <c r="B519">
@@ -4516,7 +4542,7 @@
       </c>
     </row>
     <row r="520" spans="1:2">
-      <c r="A520" s="2">
+      <c r="A520" s="3">
         <v>43322</v>
       </c>
       <c r="B520">
@@ -4524,7 +4550,7 @@
       </c>
     </row>
     <row r="521" spans="1:2">
-      <c r="A521" s="2">
+      <c r="A521" s="3">
         <v>43329</v>
       </c>
       <c r="B521">
@@ -4532,7 +4558,7 @@
       </c>
     </row>
     <row r="522" spans="1:2">
-      <c r="A522" s="2">
+      <c r="A522" s="3">
         <v>43336</v>
       </c>
       <c r="B522">
@@ -4540,7 +4566,7 @@
       </c>
     </row>
     <row r="523" spans="1:2">
-      <c r="A523" s="2">
+      <c r="A523" s="3">
         <v>43343</v>
       </c>
       <c r="B523">
@@ -4548,7 +4574,7 @@
       </c>
     </row>
     <row r="524" spans="1:2">
-      <c r="A524" s="2">
+      <c r="A524" s="3">
         <v>43350</v>
       </c>
       <c r="B524">
@@ -4556,7 +4582,7 @@
       </c>
     </row>
     <row r="525" spans="1:2">
-      <c r="A525" s="2">
+      <c r="A525" s="3">
         <v>43357</v>
       </c>
       <c r="B525">
@@ -4564,7 +4590,7 @@
       </c>
     </row>
     <row r="526" spans="1:2">
-      <c r="A526" s="2">
+      <c r="A526" s="3">
         <v>43364</v>
       </c>
       <c r="B526">
@@ -4572,7 +4598,7 @@
       </c>
     </row>
     <row r="527" spans="1:2">
-      <c r="A527" s="2">
+      <c r="A527" s="3">
         <v>43371</v>
       </c>
       <c r="B527">
@@ -4580,7 +4606,7 @@
       </c>
     </row>
     <row r="528" spans="1:2">
-      <c r="A528" s="2">
+      <c r="A528" s="3">
         <v>43378</v>
       </c>
       <c r="B528">
@@ -4588,7 +4614,7 @@
       </c>
     </row>
     <row r="529" spans="1:2">
-      <c r="A529" s="2">
+      <c r="A529" s="3">
         <v>43385</v>
       </c>
       <c r="B529">
@@ -4596,7 +4622,7 @@
       </c>
     </row>
     <row r="530" spans="1:2">
-      <c r="A530" s="2">
+      <c r="A530" s="3">
         <v>43392</v>
       </c>
       <c r="B530">
@@ -4604,7 +4630,7 @@
       </c>
     </row>
     <row r="531" spans="1:2">
-      <c r="A531" s="2">
+      <c r="A531" s="3">
         <v>43399</v>
       </c>
       <c r="B531">
@@ -4612,7 +4638,7 @@
       </c>
     </row>
     <row r="532" spans="1:2">
-      <c r="A532" s="2">
+      <c r="A532" s="3">
         <v>43406</v>
       </c>
       <c r="B532">
@@ -4620,7 +4646,7 @@
       </c>
     </row>
     <row r="533" spans="1:2">
-      <c r="A533" s="2">
+      <c r="A533" s="3">
         <v>43413</v>
       </c>
       <c r="B533">
@@ -4628,7 +4654,7 @@
       </c>
     </row>
     <row r="534" spans="1:2">
-      <c r="A534" s="2">
+      <c r="A534" s="3">
         <v>43420</v>
       </c>
       <c r="B534">
@@ -4636,7 +4662,7 @@
       </c>
     </row>
     <row r="535" spans="1:2">
-      <c r="A535" s="2">
+      <c r="A535" s="3">
         <v>43427</v>
       </c>
       <c r="B535">
@@ -4644,7 +4670,7 @@
       </c>
     </row>
     <row r="536" spans="1:2">
-      <c r="A536" s="2">
+      <c r="A536" s="3">
         <v>43434</v>
       </c>
       <c r="B536">
@@ -4652,7 +4678,7 @@
       </c>
     </row>
     <row r="537" spans="1:2">
-      <c r="A537" s="2">
+      <c r="A537" s="3">
         <v>43441</v>
       </c>
       <c r="B537">
@@ -4660,7 +4686,7 @@
       </c>
     </row>
     <row r="538" spans="1:2">
-      <c r="A538" s="2">
+      <c r="A538" s="3">
         <v>43448</v>
       </c>
       <c r="B538">
@@ -4668,7 +4694,7 @@
       </c>
     </row>
     <row r="539" spans="1:2">
-      <c r="A539" s="2">
+      <c r="A539" s="3">
         <v>43455</v>
       </c>
       <c r="B539">
@@ -4676,7 +4702,7 @@
       </c>
     </row>
     <row r="540" spans="1:2">
-      <c r="A540" s="2">
+      <c r="A540" s="3">
         <v>43462</v>
       </c>
       <c r="B540">
@@ -4684,7 +4710,7 @@
       </c>
     </row>
     <row r="541" spans="1:2">
-      <c r="A541" s="2">
+      <c r="A541" s="3">
         <v>43469</v>
       </c>
       <c r="B541">
@@ -4692,7 +4718,7 @@
       </c>
     </row>
     <row r="542" spans="1:2">
-      <c r="A542" s="2">
+      <c r="A542" s="3">
         <v>43476</v>
       </c>
       <c r="B542">
@@ -4700,7 +4726,7 @@
       </c>
     </row>
     <row r="543" spans="1:2">
-      <c r="A543" s="2">
+      <c r="A543" s="3">
         <v>43483</v>
       </c>
       <c r="B543">
@@ -4708,7 +4734,7 @@
       </c>
     </row>
     <row r="544" spans="1:2">
-      <c r="A544" s="2">
+      <c r="A544" s="3">
         <v>43490</v>
       </c>
       <c r="B544">
@@ -4716,7 +4742,7 @@
       </c>
     </row>
     <row r="545" spans="1:2">
-      <c r="A545" s="2">
+      <c r="A545" s="3">
         <v>43497</v>
       </c>
       <c r="B545">
@@ -4724,7 +4750,7 @@
       </c>
     </row>
     <row r="546" spans="1:2">
-      <c r="A546" s="2">
+      <c r="A546" s="3">
         <v>43504</v>
       </c>
       <c r="B546">
@@ -4732,7 +4758,7 @@
       </c>
     </row>
     <row r="547" spans="1:2">
-      <c r="A547" s="2">
+      <c r="A547" s="3">
         <v>43511</v>
       </c>
       <c r="B547">
@@ -4740,7 +4766,7 @@
       </c>
     </row>
     <row r="548" spans="1:2">
-      <c r="A548" s="2">
+      <c r="A548" s="3">
         <v>43518</v>
       </c>
       <c r="B548">
@@ -4748,7 +4774,7 @@
       </c>
     </row>
     <row r="549" spans="1:2">
-      <c r="A549" s="2">
+      <c r="A549" s="3">
         <v>43525</v>
       </c>
       <c r="B549">
@@ -4756,7 +4782,7 @@
       </c>
     </row>
     <row r="550" spans="1:2">
-      <c r="A550" s="2">
+      <c r="A550" s="3">
         <v>43532</v>
       </c>
       <c r="B550">
@@ -4764,7 +4790,7 @@
       </c>
     </row>
     <row r="551" spans="1:2">
-      <c r="A551" s="2">
+      <c r="A551" s="3">
         <v>43539</v>
       </c>
       <c r="B551">
@@ -4772,7 +4798,7 @@
       </c>
     </row>
     <row r="552" spans="1:2">
-      <c r="A552" s="2">
+      <c r="A552" s="3">
         <v>43546</v>
       </c>
       <c r="B552">
@@ -4780,7 +4806,7 @@
       </c>
     </row>
     <row r="553" spans="1:2">
-      <c r="A553" s="2">
+      <c r="A553" s="3">
         <v>43553</v>
       </c>
       <c r="B553">
@@ -4788,7 +4814,7 @@
       </c>
     </row>
     <row r="554" spans="1:2">
-      <c r="A554" s="2">
+      <c r="A554" s="3">
         <v>43560</v>
       </c>
       <c r="B554">
@@ -4796,7 +4822,7 @@
       </c>
     </row>
     <row r="555" spans="1:2">
-      <c r="A555" s="2">
+      <c r="A555" s="3">
         <v>43567</v>
       </c>
       <c r="B555">
@@ -4804,7 +4830,7 @@
       </c>
     </row>
     <row r="556" spans="1:2">
-      <c r="A556" s="2">
+      <c r="A556" s="3">
         <v>43574</v>
       </c>
       <c r="B556">
@@ -4812,7 +4838,7 @@
       </c>
     </row>
     <row r="557" spans="1:2">
-      <c r="A557" s="2">
+      <c r="A557" s="3">
         <v>43581</v>
       </c>
       <c r="B557">
@@ -4820,7 +4846,7 @@
       </c>
     </row>
     <row r="558" spans="1:2">
-      <c r="A558" s="2">
+      <c r="A558" s="3">
         <v>43588</v>
       </c>
       <c r="B558">
@@ -4828,7 +4854,7 @@
       </c>
     </row>
     <row r="559" spans="1:2">
-      <c r="A559" s="2">
+      <c r="A559" s="3">
         <v>43595</v>
       </c>
       <c r="B559">
@@ -4836,7 +4862,7 @@
       </c>
     </row>
     <row r="560" spans="1:2">
-      <c r="A560" s="2">
+      <c r="A560" s="3">
         <v>43602</v>
       </c>
       <c r="B560">
@@ -4844,7 +4870,7 @@
       </c>
     </row>
     <row r="561" spans="1:2">
-      <c r="A561" s="2">
+      <c r="A561" s="3">
         <v>43609</v>
       </c>
       <c r="B561">
@@ -4852,7 +4878,7 @@
       </c>
     </row>
     <row r="562" spans="1:2">
-      <c r="A562" s="2">
+      <c r="A562" s="3">
         <v>43616</v>
       </c>
       <c r="B562">
@@ -4860,7 +4886,7 @@
       </c>
     </row>
     <row r="563" spans="1:2">
-      <c r="A563" s="2">
+      <c r="A563" s="3">
         <v>43623</v>
       </c>
       <c r="B563">
@@ -4868,7 +4894,7 @@
       </c>
     </row>
     <row r="564" spans="1:2">
-      <c r="A564" s="2">
+      <c r="A564" s="3">
         <v>43630</v>
       </c>
       <c r="B564">
@@ -4876,7 +4902,7 @@
       </c>
     </row>
     <row r="565" spans="1:2">
-      <c r="A565" s="2">
+      <c r="A565" s="3">
         <v>43637</v>
       </c>
       <c r="B565">
@@ -4884,7 +4910,7 @@
       </c>
     </row>
     <row r="566" spans="1:2">
-      <c r="A566" s="2">
+      <c r="A566" s="3">
         <v>43644</v>
       </c>
       <c r="B566">
@@ -4892,7 +4918,7 @@
       </c>
     </row>
     <row r="567" spans="1:2">
-      <c r="A567" s="2">
+      <c r="A567" s="3">
         <v>43651</v>
       </c>
       <c r="B567">
@@ -4900,7 +4926,7 @@
       </c>
     </row>
     <row r="568" spans="1:2">
-      <c r="A568" s="2">
+      <c r="A568" s="3">
         <v>43658</v>
       </c>
       <c r="B568">
@@ -4908,7 +4934,7 @@
       </c>
     </row>
     <row r="569" spans="1:2">
-      <c r="A569" s="2">
+      <c r="A569" s="3">
         <v>43665</v>
       </c>
       <c r="B569">
@@ -4916,7 +4942,7 @@
       </c>
     </row>
     <row r="570" spans="1:2">
-      <c r="A570" s="2">
+      <c r="A570" s="3">
         <v>43672</v>
       </c>
       <c r="B570">
@@ -4924,7 +4950,7 @@
       </c>
     </row>
     <row r="571" spans="1:2">
-      <c r="A571" s="2">
+      <c r="A571" s="3">
         <v>43679</v>
       </c>
       <c r="B571">
@@ -4932,7 +4958,7 @@
       </c>
     </row>
     <row r="572" spans="1:2">
-      <c r="A572" s="2">
+      <c r="A572" s="3">
         <v>43686</v>
       </c>
       <c r="B572">
@@ -4940,7 +4966,7 @@
       </c>
     </row>
     <row r="573" spans="1:2">
-      <c r="A573" s="2">
+      <c r="A573" s="3">
         <v>43693</v>
       </c>
       <c r="B573">
@@ -4948,7 +4974,7 @@
       </c>
     </row>
     <row r="574" spans="1:2">
-      <c r="A574" s="2">
+      <c r="A574" s="3">
         <v>43700</v>
       </c>
       <c r="B574">
@@ -4956,7 +4982,7 @@
       </c>
     </row>
     <row r="575" spans="1:2">
-      <c r="A575" s="2">
+      <c r="A575" s="3">
         <v>43707</v>
       </c>
       <c r="B575">
@@ -4964,7 +4990,7 @@
       </c>
     </row>
     <row r="576" spans="1:2">
-      <c r="A576" s="2">
+      <c r="A576" s="3">
         <v>43714</v>
       </c>
       <c r="B576">
@@ -4972,7 +4998,7 @@
       </c>
     </row>
     <row r="577" spans="1:2">
-      <c r="A577" s="2">
+      <c r="A577" s="3">
         <v>43721</v>
       </c>
       <c r="B577">
@@ -4980,7 +5006,7 @@
       </c>
     </row>
     <row r="578" spans="1:2">
-      <c r="A578" s="2">
+      <c r="A578" s="3">
         <v>43728</v>
       </c>
       <c r="B578">
@@ -4988,7 +5014,7 @@
       </c>
     </row>
     <row r="579" spans="1:2">
-      <c r="A579" s="2">
+      <c r="A579" s="3">
         <v>43735</v>
       </c>
       <c r="B579">
@@ -4996,7 +5022,7 @@
       </c>
     </row>
     <row r="580" spans="1:2">
-      <c r="A580" s="2">
+      <c r="A580" s="3">
         <v>43742</v>
       </c>
       <c r="B580">
@@ -5004,7 +5030,7 @@
       </c>
     </row>
     <row r="581" spans="1:2">
-      <c r="A581" s="2">
+      <c r="A581" s="3">
         <v>43749</v>
       </c>
       <c r="B581">
@@ -5012,7 +5038,7 @@
       </c>
     </row>
     <row r="582" spans="1:2">
-      <c r="A582" s="2">
+      <c r="A582" s="3">
         <v>43756</v>
       </c>
       <c r="B582">
@@ -5020,7 +5046,7 @@
       </c>
     </row>
     <row r="583" spans="1:2">
-      <c r="A583" s="2">
+      <c r="A583" s="3">
         <v>43763</v>
       </c>
       <c r="B583">
@@ -5028,7 +5054,7 @@
       </c>
     </row>
     <row r="584" spans="1:2">
-      <c r="A584" s="2">
+      <c r="A584" s="3">
         <v>43770</v>
       </c>
       <c r="B584">
@@ -5036,7 +5062,7 @@
       </c>
     </row>
     <row r="585" spans="1:2">
-      <c r="A585" s="2">
+      <c r="A585" s="3">
         <v>43777</v>
       </c>
       <c r="B585">
@@ -5044,7 +5070,7 @@
       </c>
     </row>
     <row r="586" spans="1:2">
-      <c r="A586" s="2">
+      <c r="A586" s="3">
         <v>43784</v>
       </c>
       <c r="B586">
@@ -5052,7 +5078,7 @@
       </c>
     </row>
     <row r="587" spans="1:2">
-      <c r="A587" s="2">
+      <c r="A587" s="3">
         <v>43791</v>
       </c>
       <c r="B587">
@@ -5060,7 +5086,7 @@
       </c>
     </row>
     <row r="588" spans="1:2">
-      <c r="A588" s="2">
+      <c r="A588" s="3">
         <v>43798</v>
       </c>
       <c r="B588">
@@ -5068,7 +5094,7 @@
       </c>
     </row>
     <row r="589" spans="1:2">
-      <c r="A589" s="2">
+      <c r="A589" s="3">
         <v>43805</v>
       </c>
       <c r="B589">
@@ -5076,7 +5102,7 @@
       </c>
     </row>
     <row r="590" spans="1:2">
-      <c r="A590" s="2">
+      <c r="A590" s="3">
         <v>43812</v>
       </c>
       <c r="B590">
@@ -5084,7 +5110,7 @@
       </c>
     </row>
     <row r="591" spans="1:2">
-      <c r="A591" s="2">
+      <c r="A591" s="3">
         <v>43819</v>
       </c>
       <c r="B591">
@@ -5092,7 +5118,7 @@
       </c>
     </row>
     <row r="592" spans="1:2">
-      <c r="A592" s="2">
+      <c r="A592" s="3">
         <v>43826</v>
       </c>
       <c r="B592">
@@ -5100,7 +5126,7 @@
       </c>
     </row>
     <row r="593" spans="1:2">
-      <c r="A593" s="2">
+      <c r="A593" s="3">
         <v>43833</v>
       </c>
       <c r="B593">
@@ -5108,7 +5134,7 @@
       </c>
     </row>
     <row r="594" spans="1:2">
-      <c r="A594" s="2">
+      <c r="A594" s="3">
         <v>43840</v>
       </c>
       <c r="B594">
@@ -5116,7 +5142,7 @@
       </c>
     </row>
     <row r="595" spans="1:2">
-      <c r="A595" s="2">
+      <c r="A595" s="3">
         <v>43847</v>
       </c>
       <c r="B595">
@@ -5124,7 +5150,7 @@
       </c>
     </row>
     <row r="596" spans="1:2">
-      <c r="A596" s="2">
+      <c r="A596" s="3">
         <v>43854</v>
       </c>
       <c r="B596">
@@ -5132,7 +5158,7 @@
       </c>
     </row>
     <row r="597" spans="1:2">
-      <c r="A597" s="2">
+      <c r="A597" s="3">
         <v>43861</v>
       </c>
       <c r="B597">
@@ -5140,7 +5166,7 @@
       </c>
     </row>
     <row r="598" spans="1:2">
-      <c r="A598" s="2">
+      <c r="A598" s="3">
         <v>43868</v>
       </c>
       <c r="B598">
@@ -5148,7 +5174,7 @@
       </c>
     </row>
     <row r="599" spans="1:2">
-      <c r="A599" s="2">
+      <c r="A599" s="3">
         <v>43875</v>
       </c>
       <c r="B599">
@@ -5156,7 +5182,7 @@
       </c>
     </row>
     <row r="600" spans="1:2">
-      <c r="A600" s="2">
+      <c r="A600" s="3">
         <v>43882</v>
       </c>
       <c r="B600">
@@ -5164,7 +5190,7 @@
       </c>
     </row>
     <row r="601" spans="1:2">
-      <c r="A601" s="2">
+      <c r="A601" s="3">
         <v>43889</v>
       </c>
       <c r="B601">
@@ -5172,7 +5198,7 @@
       </c>
     </row>
     <row r="602" spans="1:2">
-      <c r="A602" s="2">
+      <c r="A602" s="3">
         <v>43896</v>
       </c>
       <c r="B602">
@@ -5180,7 +5206,7 @@
       </c>
     </row>
     <row r="603" spans="1:2">
-      <c r="A603" s="2">
+      <c r="A603" s="3">
         <v>43903</v>
       </c>
       <c r="B603">
@@ -5188,7 +5214,7 @@
       </c>
     </row>
     <row r="604" spans="1:2">
-      <c r="A604" s="2">
+      <c r="A604" s="3">
         <v>43910</v>
       </c>
       <c r="B604">
@@ -5196,7 +5222,7 @@
       </c>
     </row>
     <row r="605" spans="1:2">
-      <c r="A605" s="2">
+      <c r="A605" s="3">
         <v>43917</v>
       </c>
       <c r="B605">
@@ -5204,7 +5230,7 @@
       </c>
     </row>
     <row r="606" spans="1:2">
-      <c r="A606" s="2">
+      <c r="A606" s="3">
         <v>43924</v>
       </c>
       <c r="B606">
@@ -5212,7 +5238,7 @@
       </c>
     </row>
     <row r="607" spans="1:2">
-      <c r="A607" s="2">
+      <c r="A607" s="3">
         <v>43931</v>
       </c>
       <c r="B607">
@@ -5220,7 +5246,7 @@
       </c>
     </row>
     <row r="608" spans="1:2">
-      <c r="A608" s="2">
+      <c r="A608" s="3">
         <v>43938</v>
       </c>
       <c r="B608">
@@ -5228,7 +5254,7 @@
       </c>
     </row>
     <row r="609" spans="1:2">
-      <c r="A609" s="2">
+      <c r="A609" s="3">
         <v>43945</v>
       </c>
       <c r="B609">
@@ -5236,7 +5262,7 @@
       </c>
     </row>
     <row r="610" spans="1:2">
-      <c r="A610" s="2">
+      <c r="A610" s="3">
         <v>43952</v>
       </c>
       <c r="B610">
@@ -5244,7 +5270,7 @@
       </c>
     </row>
     <row r="611" spans="1:2">
-      <c r="A611" s="2">
+      <c r="A611" s="3">
         <v>43959</v>
       </c>
       <c r="B611">
@@ -5252,7 +5278,7 @@
       </c>
     </row>
     <row r="612" spans="1:2">
-      <c r="A612" s="2">
+      <c r="A612" s="3">
         <v>43966</v>
       </c>
       <c r="B612">
@@ -5260,7 +5286,7 @@
       </c>
     </row>
     <row r="613" spans="1:2">
-      <c r="A613" s="2">
+      <c r="A613" s="3">
         <v>43973</v>
       </c>
       <c r="B613">
@@ -5268,7 +5294,7 @@
       </c>
     </row>
     <row r="614" spans="1:2">
-      <c r="A614" s="2">
+      <c r="A614" s="3">
         <v>43980</v>
       </c>
       <c r="B614">
@@ -5276,7 +5302,7 @@
       </c>
     </row>
     <row r="615" spans="1:2">
-      <c r="A615" s="2">
+      <c r="A615" s="3">
         <v>43987</v>
       </c>
       <c r="B615">
@@ -5284,7 +5310,7 @@
       </c>
     </row>
     <row r="616" spans="1:2">
-      <c r="A616" s="2">
+      <c r="A616" s="3">
         <v>43994</v>
       </c>
       <c r="B616">
@@ -5292,7 +5318,7 @@
       </c>
     </row>
     <row r="617" spans="1:2">
-      <c r="A617" s="2">
+      <c r="A617" s="3">
         <v>44001</v>
       </c>
       <c r="B617">
@@ -5300,7 +5326,7 @@
       </c>
     </row>
     <row r="618" spans="1:2">
-      <c r="A618" s="2">
+      <c r="A618" s="3">
         <v>44008</v>
       </c>
       <c r="B618">
@@ -5308,7 +5334,7 @@
       </c>
     </row>
     <row r="619" spans="1:2">
-      <c r="A619" s="2">
+      <c r="A619" s="3">
         <v>44015</v>
       </c>
       <c r="B619">
@@ -5316,7 +5342,7 @@
       </c>
     </row>
     <row r="620" spans="1:2">
-      <c r="A620" s="2">
+      <c r="A620" s="3">
         <v>44022</v>
       </c>
       <c r="B620">
@@ -5324,7 +5350,7 @@
       </c>
     </row>
     <row r="621" spans="1:2">
-      <c r="A621" s="2">
+      <c r="A621" s="3">
         <v>44029</v>
       </c>
       <c r="B621">
@@ -5332,7 +5358,7 @@
       </c>
     </row>
     <row r="622" spans="1:2">
-      <c r="A622" s="2">
+      <c r="A622" s="3">
         <v>44036</v>
       </c>
       <c r="B622">
@@ -5340,7 +5366,7 @@
       </c>
     </row>
     <row r="623" spans="1:2">
-      <c r="A623" s="2">
+      <c r="A623" s="3">
         <v>44043</v>
       </c>
       <c r="B623">
@@ -5348,7 +5374,7 @@
       </c>
     </row>
     <row r="624" spans="1:2">
-      <c r="A624" s="2">
+      <c r="A624" s="3">
         <v>44050</v>
       </c>
       <c r="B624">
@@ -5356,7 +5382,7 @@
       </c>
     </row>
     <row r="625" spans="1:2">
-      <c r="A625" s="2">
+      <c r="A625" s="3">
         <v>44057</v>
       </c>
       <c r="B625">
@@ -5364,7 +5390,7 @@
       </c>
     </row>
     <row r="626" spans="1:2">
-      <c r="A626" s="2">
+      <c r="A626" s="3">
         <v>44064</v>
       </c>
       <c r="B626">
@@ -5372,7 +5398,7 @@
       </c>
     </row>
     <row r="627" spans="1:2">
-      <c r="A627" s="2">
+      <c r="A627" s="3">
         <v>44071</v>
       </c>
       <c r="B627">
@@ -5380,7 +5406,7 @@
       </c>
     </row>
     <row r="628" spans="1:2">
-      <c r="A628" s="2">
+      <c r="A628" s="3">
         <v>44078</v>
       </c>
       <c r="B628">
@@ -5388,7 +5414,7 @@
       </c>
     </row>
     <row r="629" spans="1:2">
-      <c r="A629" s="2">
+      <c r="A629" s="3">
         <v>44085</v>
       </c>
       <c r="B629">
@@ -5396,7 +5422,7 @@
       </c>
     </row>
     <row r="630" spans="1:2">
-      <c r="A630" s="2">
+      <c r="A630" s="3">
         <v>44092</v>
       </c>
       <c r="B630">
@@ -5404,7 +5430,7 @@
       </c>
     </row>
     <row r="631" spans="1:2">
-      <c r="A631" s="2">
+      <c r="A631" s="3">
         <v>44099</v>
       </c>
       <c r="B631">
@@ -5412,7 +5438,7 @@
       </c>
     </row>
     <row r="632" spans="1:2">
-      <c r="A632" s="2">
+      <c r="A632" s="3">
         <v>44106</v>
       </c>
       <c r="B632">
@@ -5420,7 +5446,7 @@
       </c>
     </row>
     <row r="633" spans="1:2">
-      <c r="A633" s="2">
+      <c r="A633" s="3">
         <v>44113</v>
       </c>
       <c r="B633">
@@ -5428,7 +5454,7 @@
       </c>
     </row>
     <row r="634" spans="1:2">
-      <c r="A634" s="2">
+      <c r="A634" s="3">
         <v>44120</v>
       </c>
       <c r="B634">
@@ -5436,7 +5462,7 @@
       </c>
     </row>
     <row r="635" spans="1:2">
-      <c r="A635" s="2">
+      <c r="A635" s="3">
         <v>44127</v>
       </c>
       <c r="B635">
@@ -5444,7 +5470,7 @@
       </c>
     </row>
     <row r="636" spans="1:2">
-      <c r="A636" s="2">
+      <c r="A636" s="3">
         <v>44134</v>
       </c>
       <c r="B636">
@@ -5452,7 +5478,7 @@
       </c>
     </row>
     <row r="637" spans="1:2">
-      <c r="A637" s="2">
+      <c r="A637" s="3">
         <v>44141</v>
       </c>
       <c r="B637">
@@ -5460,7 +5486,7 @@
       </c>
     </row>
     <row r="638" spans="1:2">
-      <c r="A638" s="2">
+      <c r="A638" s="3">
         <v>44148</v>
       </c>
       <c r="B638">
@@ -5468,7 +5494,7 @@
       </c>
     </row>
     <row r="639" spans="1:2">
-      <c r="A639" s="2">
+      <c r="A639" s="3">
         <v>44155</v>
       </c>
       <c r="B639">
@@ -5476,7 +5502,7 @@
       </c>
     </row>
     <row r="640" spans="1:2">
-      <c r="A640" s="2">
+      <c r="A640" s="3">
         <v>44162</v>
       </c>
       <c r="B640">
@@ -5484,7 +5510,7 @@
       </c>
     </row>
     <row r="641" spans="1:2">
-      <c r="A641" s="2">
+      <c r="A641" s="3">
         <v>44169</v>
       </c>
       <c r="B641">
@@ -5492,7 +5518,7 @@
       </c>
     </row>
     <row r="642" spans="1:2">
-      <c r="A642" s="2">
+      <c r="A642" s="3">
         <v>44176</v>
       </c>
       <c r="B642">
@@ -5500,7 +5526,7 @@
       </c>
     </row>
     <row r="643" spans="1:2">
-      <c r="A643" s="2">
+      <c r="A643" s="3">
         <v>44183</v>
       </c>
       <c r="B643">
@@ -5508,7 +5534,7 @@
       </c>
     </row>
     <row r="644" spans="1:2">
-      <c r="A644" s="2">
+      <c r="A644" s="3">
         <v>44190</v>
       </c>
       <c r="B644">
@@ -5516,7 +5542,7 @@
       </c>
     </row>
     <row r="645" spans="1:2">
-      <c r="A645" s="2">
+      <c r="A645" s="3">
         <v>44197</v>
       </c>
       <c r="B645">
@@ -5524,7 +5550,7 @@
       </c>
     </row>
     <row r="646" spans="1:2">
-      <c r="A646" s="2">
+      <c r="A646" s="3">
         <v>44204</v>
       </c>
       <c r="B646">
@@ -5532,7 +5558,7 @@
       </c>
     </row>
     <row r="647" spans="1:2">
-      <c r="A647" s="2">
+      <c r="A647" s="3">
         <v>44211</v>
       </c>
       <c r="B647">
@@ -5540,7 +5566,7 @@
       </c>
     </row>
     <row r="648" spans="1:2">
-      <c r="A648" s="2">
+      <c r="A648" s="3">
         <v>44218</v>
       </c>
       <c r="B648">
@@ -5548,7 +5574,7 @@
       </c>
     </row>
     <row r="649" spans="1:2">
-      <c r="A649" s="2">
+      <c r="A649" s="3">
         <v>44225</v>
       </c>
       <c r="B649">
@@ -5556,7 +5582,7 @@
       </c>
     </row>
     <row r="650" spans="1:2">
-      <c r="A650" s="2">
+      <c r="A650" s="3">
         <v>44232</v>
       </c>
       <c r="B650">
@@ -5564,7 +5590,7 @@
       </c>
     </row>
     <row r="651" spans="1:2">
-      <c r="A651" s="2">
+      <c r="A651" s="3">
         <v>44239</v>
       </c>
       <c r="B651">
@@ -5572,7 +5598,7 @@
       </c>
     </row>
     <row r="652" spans="1:2">
-      <c r="A652" s="2">
+      <c r="A652" s="3">
         <v>44246</v>
       </c>
       <c r="B652">
@@ -5580,7 +5606,7 @@
       </c>
     </row>
     <row r="653" spans="1:2">
-      <c r="A653" s="2">
+      <c r="A653" s="3">
         <v>44253</v>
       </c>
       <c r="B653">
@@ -5588,7 +5614,7 @@
       </c>
     </row>
     <row r="654" spans="1:2">
-      <c r="A654" s="2">
+      <c r="A654" s="3">
         <v>44260</v>
       </c>
       <c r="B654">
@@ -5596,7 +5622,7 @@
       </c>
     </row>
     <row r="655" spans="1:2">
-      <c r="A655" s="2">
+      <c r="A655" s="3">
         <v>44267</v>
       </c>
       <c r="B655">
@@ -5604,7 +5630,7 @@
       </c>
     </row>
     <row r="656" spans="1:2">
-      <c r="A656" s="2">
+      <c r="A656" s="3">
         <v>44274</v>
       </c>
       <c r="B656">
@@ -5612,7 +5638,7 @@
       </c>
     </row>
     <row r="657" spans="1:2">
-      <c r="A657" s="2">
+      <c r="A657" s="3">
         <v>44281</v>
       </c>
       <c r="B657">
@@ -5620,7 +5646,7 @@
       </c>
     </row>
     <row r="658" spans="1:2">
-      <c r="A658" s="2">
+      <c r="A658" s="3">
         <v>44288</v>
       </c>
       <c r="B658">
@@ -5628,7 +5654,7 @@
       </c>
     </row>
     <row r="659" spans="1:2">
-      <c r="A659" s="2">
+      <c r="A659" s="3">
         <v>44295</v>
       </c>
       <c r="B659">
@@ -5636,7 +5662,7 @@
       </c>
     </row>
     <row r="660" spans="1:2">
-      <c r="A660" s="2">
+      <c r="A660" s="3">
         <v>44302</v>
       </c>
       <c r="B660">
@@ -5644,7 +5670,7 @@
       </c>
     </row>
     <row r="661" spans="1:2">
-      <c r="A661" s="2">
+      <c r="A661" s="3">
         <v>44309</v>
       </c>
       <c r="B661">
@@ -5652,7 +5678,7 @@
       </c>
     </row>
     <row r="662" spans="1:2">
-      <c r="A662" s="2">
+      <c r="A662" s="3">
         <v>44316</v>
       </c>
       <c r="B662">
@@ -5660,7 +5686,7 @@
       </c>
     </row>
     <row r="663" spans="1:2">
-      <c r="A663" s="2">
+      <c r="A663" s="3">
         <v>44323</v>
       </c>
       <c r="B663">
@@ -5668,7 +5694,7 @@
       </c>
     </row>
     <row r="664" spans="1:2">
-      <c r="A664" s="2">
+      <c r="A664" s="3">
         <v>44330</v>
       </c>
       <c r="B664">
@@ -5676,7 +5702,7 @@
       </c>
     </row>
     <row r="665" spans="1:2">
-      <c r="A665" s="2">
+      <c r="A665" s="3">
         <v>44337</v>
       </c>
       <c r="B665">
@@ -5684,7 +5710,7 @@
       </c>
     </row>
     <row r="666" spans="1:2">
-      <c r="A666" s="2">
+      <c r="A666" s="3">
         <v>44344</v>
       </c>
       <c r="B666">
@@ -5692,7 +5718,7 @@
       </c>
     </row>
     <row r="667" spans="1:2">
-      <c r="A667" s="2">
+      <c r="A667" s="3">
         <v>44351</v>
       </c>
       <c r="B667">
@@ -5700,7 +5726,7 @@
       </c>
     </row>
     <row r="668" spans="1:2">
-      <c r="A668" s="2">
+      <c r="A668" s="3">
         <v>44358</v>
       </c>
       <c r="B668">
@@ -5708,7 +5734,7 @@
       </c>
     </row>
     <row r="669" spans="1:2">
-      <c r="A669" s="2">
+      <c r="A669" s="3">
         <v>44365</v>
       </c>
       <c r="B669">
@@ -5716,7 +5742,7 @@
       </c>
     </row>
     <row r="670" spans="1:2">
-      <c r="A670" s="2">
+      <c r="A670" s="3">
         <v>44372</v>
       </c>
       <c r="B670">
@@ -5724,7 +5750,7 @@
       </c>
     </row>
     <row r="671" spans="1:2">
-      <c r="A671" s="2">
+      <c r="A671" s="3">
         <v>44379</v>
       </c>
       <c r="B671">
@@ -5732,7 +5758,7 @@
       </c>
     </row>
     <row r="672" spans="1:2">
-      <c r="A672" s="2">
+      <c r="A672" s="3">
         <v>44386</v>
       </c>
       <c r="B672">
@@ -5740,7 +5766,7 @@
       </c>
     </row>
     <row r="673" spans="1:2">
-      <c r="A673" s="2">
+      <c r="A673" s="3">
         <v>44393</v>
       </c>
       <c r="B673">
@@ -5748,7 +5774,7 @@
       </c>
     </row>
     <row r="674" spans="1:2">
-      <c r="A674" s="2">
+      <c r="A674" s="3">
         <v>44400</v>
       </c>
       <c r="B674">
@@ -5756,7 +5782,7 @@
       </c>
     </row>
     <row r="675" spans="1:2">
-      <c r="A675" s="2">
+      <c r="A675" s="3">
         <v>44407</v>
       </c>
       <c r="B675">
@@ -5764,7 +5790,7 @@
       </c>
     </row>
     <row r="676" spans="1:2">
-      <c r="A676" s="2">
+      <c r="A676" s="3">
         <v>44414</v>
       </c>
       <c r="B676">
@@ -5772,7 +5798,7 @@
       </c>
     </row>
     <row r="677" spans="1:2">
-      <c r="A677" s="2">
+      <c r="A677" s="3">
         <v>44421</v>
       </c>
       <c r="B677">
@@ -5780,7 +5806,7 @@
       </c>
     </row>
     <row r="678" spans="1:2">
-      <c r="A678" s="2">
+      <c r="A678" s="3">
         <v>44428</v>
       </c>
       <c r="B678">
@@ -5788,7 +5814,7 @@
       </c>
     </row>
     <row r="679" spans="1:2">
-      <c r="A679" s="2">
+      <c r="A679" s="3">
         <v>44435</v>
       </c>
       <c r="B679">
@@ -5796,7 +5822,7 @@
       </c>
     </row>
     <row r="680" spans="1:2">
-      <c r="A680" s="2">
+      <c r="A680" s="3">
         <v>44442</v>
       </c>
       <c r="B680">
@@ -5804,7 +5830,7 @@
       </c>
     </row>
     <row r="681" spans="1:2">
-      <c r="A681" s="2">
+      <c r="A681" s="3">
         <v>44449</v>
       </c>
       <c r="B681">
@@ -5812,7 +5838,7 @@
       </c>
     </row>
     <row r="682" spans="1:2">
-      <c r="A682" s="2">
+      <c r="A682" s="3">
         <v>44456</v>
       </c>
       <c r="B682">
@@ -5820,7 +5846,7 @@
       </c>
     </row>
     <row r="683" spans="1:2">
-      <c r="A683" s="2">
+      <c r="A683" s="3">
         <v>44463</v>
       </c>
       <c r="B683">
@@ -5828,7 +5854,7 @@
       </c>
     </row>
     <row r="684" spans="1:2">
-      <c r="A684" s="2">
+      <c r="A684" s="3">
         <v>44470</v>
       </c>
       <c r="B684">
@@ -5836,7 +5862,7 @@
       </c>
     </row>
     <row r="685" spans="1:2">
-      <c r="A685" s="2">
+      <c r="A685" s="3">
         <v>44477</v>
       </c>
       <c r="B685">
@@ -5844,7 +5870,7 @@
       </c>
     </row>
     <row r="686" spans="1:2">
-      <c r="A686" s="2">
+      <c r="A686" s="3">
         <v>44484</v>
       </c>
       <c r="B686">
@@ -5852,7 +5878,7 @@
       </c>
     </row>
     <row r="687" spans="1:2">
-      <c r="A687" s="2">
+      <c r="A687" s="3">
         <v>44491</v>
       </c>
       <c r="B687">
@@ -5860,7 +5886,7 @@
       </c>
     </row>
     <row r="688" spans="1:2">
-      <c r="A688" s="2">
+      <c r="A688" s="3">
         <v>44498</v>
       </c>
       <c r="B688">
@@ -5868,7 +5894,7 @@
       </c>
     </row>
     <row r="689" spans="1:2">
-      <c r="A689" s="2">
+      <c r="A689" s="3">
         <v>44505</v>
       </c>
       <c r="B689">
@@ -5876,7 +5902,7 @@
       </c>
     </row>
     <row r="690" spans="1:2">
-      <c r="A690" s="2">
+      <c r="A690" s="3">
         <v>44512</v>
       </c>
       <c r="B690">
@@ -5884,7 +5910,7 @@
       </c>
     </row>
     <row r="691" spans="1:2">
-      <c r="A691" s="2">
+      <c r="A691" s="3">
         <v>44519</v>
       </c>
       <c r="B691">
@@ -5892,7 +5918,7 @@
       </c>
     </row>
     <row r="692" spans="1:2">
-      <c r="A692" s="2">
+      <c r="A692" s="3">
         <v>44526</v>
       </c>
       <c r="B692">
@@ -5900,7 +5926,7 @@
       </c>
     </row>
     <row r="693" spans="1:2">
-      <c r="A693" s="2">
+      <c r="A693" s="3">
         <v>44533</v>
       </c>
       <c r="B693">
@@ -5908,7 +5934,7 @@
       </c>
     </row>
     <row r="694" spans="1:2">
-      <c r="A694" s="2">
+      <c r="A694" s="3">
         <v>44540</v>
       </c>
       <c r="B694">
@@ -5916,7 +5942,7 @@
       </c>
     </row>
     <row r="695" spans="1:2">
-      <c r="A695" s="2">
+      <c r="A695" s="3">
         <v>44547</v>
       </c>
       <c r="B695">
@@ -5924,7 +5950,7 @@
       </c>
     </row>
     <row r="696" spans="1:2">
-      <c r="A696" s="2">
+      <c r="A696" s="3">
         <v>44554</v>
       </c>
       <c r="B696">
@@ -5932,7 +5958,7 @@
       </c>
     </row>
     <row r="697" spans="1:2">
-      <c r="A697" s="2">
+      <c r="A697" s="3">
         <v>44561</v>
       </c>
       <c r="B697">
@@ -5940,7 +5966,7 @@
       </c>
     </row>
     <row r="698" spans="1:2">
-      <c r="A698" s="2">
+      <c r="A698" s="3">
         <v>44568</v>
       </c>
       <c r="B698">
@@ -5948,7 +5974,7 @@
       </c>
     </row>
     <row r="699" spans="1:2">
-      <c r="A699" s="2">
+      <c r="A699" s="3">
         <v>44575</v>
       </c>
       <c r="B699">
@@ -5956,7 +5982,7 @@
       </c>
     </row>
     <row r="700" spans="1:2">
-      <c r="A700" s="2">
+      <c r="A700" s="3">
         <v>44582</v>
       </c>
       <c r="B700">
@@ -5964,7 +5990,7 @@
       </c>
     </row>
     <row r="701" spans="1:2">
-      <c r="A701" s="2">
+      <c r="A701" s="3">
         <v>44589</v>
       </c>
       <c r="B701">
@@ -5972,7 +5998,7 @@
       </c>
     </row>
     <row r="702" spans="1:2">
-      <c r="A702" s="2">
+      <c r="A702" s="3">
         <v>44596</v>
       </c>
       <c r="B702">
@@ -5980,7 +6006,7 @@
       </c>
     </row>
     <row r="703" spans="1:2">
-      <c r="A703" s="2">
+      <c r="A703" s="3">
         <v>44603</v>
       </c>
       <c r="B703">
@@ -5988,7 +6014,7 @@
       </c>
     </row>
     <row r="704" spans="1:2">
-      <c r="A704" s="2">
+      <c r="A704" s="3">
         <v>44610</v>
       </c>
       <c r="B704">
@@ -5996,7 +6022,7 @@
       </c>
     </row>
     <row r="705" spans="1:2">
-      <c r="A705" s="2">
+      <c r="A705" s="3">
         <v>44617</v>
       </c>
       <c r="B705">
@@ -6004,7 +6030,7 @@
       </c>
     </row>
     <row r="706" spans="1:2">
-      <c r="A706" s="2">
+      <c r="A706" s="3">
         <v>44624</v>
       </c>
       <c r="B706">
@@ -6012,7 +6038,7 @@
       </c>
     </row>
     <row r="707" spans="1:2">
-      <c r="A707" s="2">
+      <c r="A707" s="3">
         <v>44631</v>
       </c>
       <c r="B707">
@@ -6020,7 +6046,7 @@
       </c>
     </row>
     <row r="708" spans="1:2">
-      <c r="A708" s="2">
+      <c r="A708" s="3">
         <v>44638</v>
       </c>
       <c r="B708">
@@ -6028,7 +6054,7 @@
       </c>
     </row>
     <row r="709" spans="1:2">
-      <c r="A709" s="2">
+      <c r="A709" s="3">
         <v>44645</v>
       </c>
       <c r="B709">
@@ -6036,7 +6062,7 @@
       </c>
     </row>
     <row r="710" spans="1:2">
-      <c r="A710" s="2">
+      <c r="A710" s="3">
         <v>44652</v>
       </c>
       <c r="B710">
@@ -6044,7 +6070,7 @@
       </c>
     </row>
     <row r="711" spans="1:2">
-      <c r="A711" s="2">
+      <c r="A711" s="3">
         <v>44659</v>
       </c>
       <c r="B711">
@@ -6052,7 +6078,7 @@
       </c>
     </row>
     <row r="712" spans="1:2">
-      <c r="A712" s="2">
+      <c r="A712" s="3">
         <v>44666</v>
       </c>
       <c r="B712">
@@ -6060,7 +6086,7 @@
       </c>
     </row>
     <row r="713" spans="1:2">
-      <c r="A713" s="2">
+      <c r="A713" s="3">
         <v>44673</v>
       </c>
       <c r="B713">
@@ -6068,7 +6094,7 @@
       </c>
     </row>
     <row r="714" spans="1:2">
-      <c r="A714" s="2">
+      <c r="A714" s="3">
         <v>44680</v>
       </c>
       <c r="B714">
@@ -6076,7 +6102,7 @@
       </c>
     </row>
     <row r="715" spans="1:2">
-      <c r="A715" s="2">
+      <c r="A715" s="3">
         <v>44687</v>
       </c>
       <c r="B715">
@@ -6084,7 +6110,7 @@
       </c>
     </row>
     <row r="716" spans="1:2">
-      <c r="A716" s="2">
+      <c r="A716" s="3">
         <v>44694</v>
       </c>
       <c r="B716">
@@ -6092,7 +6118,7 @@
       </c>
     </row>
     <row r="717" spans="1:2">
-      <c r="A717" s="2">
+      <c r="A717" s="3">
         <v>44701</v>
       </c>
       <c r="B717">
@@ -6100,7 +6126,7 @@
       </c>
     </row>
     <row r="718" spans="1:2">
-      <c r="A718" s="2">
+      <c r="A718" s="3">
         <v>44708</v>
       </c>
       <c r="B718">
@@ -6108,7 +6134,7 @@
       </c>
     </row>
     <row r="719" spans="1:2">
-      <c r="A719" s="2">
+      <c r="A719" s="3">
         <v>44715</v>
       </c>
       <c r="B719">
@@ -6116,7 +6142,7 @@
       </c>
     </row>
     <row r="720" spans="1:2">
-      <c r="A720" s="2">
+      <c r="A720" s="3">
         <v>44722</v>
       </c>
       <c r="B720">
@@ -6124,7 +6150,7 @@
       </c>
     </row>
     <row r="721" spans="1:2">
-      <c r="A721" s="2">
+      <c r="A721" s="3">
         <v>44729</v>
       </c>
       <c r="B721">
@@ -6132,7 +6158,7 @@
       </c>
     </row>
     <row r="722" spans="1:2">
-      <c r="A722" s="2">
+      <c r="A722" s="3">
         <v>44736</v>
       </c>
       <c r="B722">
@@ -6140,7 +6166,7 @@
       </c>
     </row>
     <row r="723" spans="1:2">
-      <c r="A723" s="2">
+      <c r="A723" s="3">
         <v>44743</v>
       </c>
       <c r="B723">
@@ -6148,7 +6174,7 @@
       </c>
     </row>
     <row r="724" spans="1:2">
-      <c r="A724" s="2">
+      <c r="A724" s="3">
         <v>44750</v>
       </c>
       <c r="B724">
@@ -6156,7 +6182,7 @@
       </c>
     </row>
     <row r="725" spans="1:2">
-      <c r="A725" s="2">
+      <c r="A725" s="3">
         <v>44757</v>
       </c>
       <c r="B725">
@@ -6164,7 +6190,7 @@
       </c>
     </row>
     <row r="726" spans="1:2">
-      <c r="A726" s="2">
+      <c r="A726" s="3">
         <v>44764</v>
       </c>
       <c r="B726">
@@ -6172,7 +6198,7 @@
       </c>
     </row>
     <row r="727" spans="1:2">
-      <c r="A727" s="2">
+      <c r="A727" s="3">
         <v>44771</v>
       </c>
       <c r="B727">
@@ -6180,7 +6206,7 @@
       </c>
     </row>
     <row r="728" spans="1:2">
-      <c r="A728" s="2">
+      <c r="A728" s="3">
         <v>44778</v>
       </c>
       <c r="B728">
@@ -6188,7 +6214,7 @@
       </c>
     </row>
     <row r="729" spans="1:2">
-      <c r="A729" s="2">
+      <c r="A729" s="3">
         <v>44785</v>
       </c>
       <c r="B729">
@@ -6196,7 +6222,7 @@
       </c>
     </row>
     <row r="730" spans="1:2">
-      <c r="A730" s="2">
+      <c r="A730" s="3">
         <v>44792</v>
       </c>
       <c r="B730">
@@ -6204,7 +6230,7 @@
       </c>
     </row>
     <row r="731" spans="1:2">
-      <c r="A731" s="2">
+      <c r="A731" s="3">
         <v>44799</v>
       </c>
       <c r="B731">
@@ -6212,7 +6238,7 @@
       </c>
     </row>
     <row r="732" spans="1:2">
-      <c r="A732" s="2">
+      <c r="A732" s="3">
         <v>44806</v>
       </c>
       <c r="B732">
@@ -6220,7 +6246,7 @@
       </c>
     </row>
     <row r="733" spans="1:2">
-      <c r="A733" s="2">
+      <c r="A733" s="3">
         <v>44813</v>
       </c>
       <c r="B733">
@@ -6228,7 +6254,7 @@
       </c>
     </row>
     <row r="734" spans="1:2">
-      <c r="A734" s="2">
+      <c r="A734" s="3">
         <v>44820</v>
       </c>
       <c r="B734">
@@ -6236,7 +6262,7 @@
       </c>
     </row>
     <row r="735" spans="1:2">
-      <c r="A735" s="2">
+      <c r="A735" s="3">
         <v>44827</v>
       </c>
       <c r="B735">
@@ -6244,7 +6270,7 @@
       </c>
     </row>
     <row r="736" spans="1:2">
-      <c r="A736" s="2">
+      <c r="A736" s="3">
         <v>44834</v>
       </c>
       <c r="B736">
@@ -6252,7 +6278,7 @@
       </c>
     </row>
     <row r="737" spans="1:2">
-      <c r="A737" s="2">
+      <c r="A737" s="3">
         <v>44841</v>
       </c>
       <c r="B737">
@@ -6260,7 +6286,7 @@
       </c>
     </row>
     <row r="738" spans="1:2">
-      <c r="A738" s="2">
+      <c r="A738" s="3">
         <v>44848</v>
       </c>
       <c r="B738">
@@ -6268,7 +6294,7 @@
       </c>
     </row>
     <row r="739" spans="1:2">
-      <c r="A739" s="2">
+      <c r="A739" s="3">
         <v>44855</v>
       </c>
       <c r="B739">
@@ -6276,7 +6302,7 @@
       </c>
     </row>
     <row r="740" spans="1:2">
-      <c r="A740" s="2">
+      <c r="A740" s="3">
         <v>44862</v>
       </c>
       <c r="B740">
@@ -6284,7 +6310,7 @@
       </c>
     </row>
     <row r="741" spans="1:2">
-      <c r="A741" s="2">
+      <c r="A741" s="3">
         <v>44869</v>
       </c>
       <c r="B741">
@@ -6292,7 +6318,7 @@
       </c>
     </row>
     <row r="742" spans="1:2">
-      <c r="A742" s="2">
+      <c r="A742" s="3">
         <v>44876</v>
       </c>
       <c r="B742">
@@ -6300,7 +6326,7 @@
       </c>
     </row>
     <row r="743" spans="1:2">
-      <c r="A743" s="2">
+      <c r="A743" s="3">
         <v>44883</v>
       </c>
       <c r="B743">
@@ -6308,7 +6334,7 @@
       </c>
     </row>
     <row r="744" spans="1:2">
-      <c r="A744" s="2">
+      <c r="A744" s="3">
         <v>44890</v>
       </c>
       <c r="B744">
@@ -6316,7 +6342,7 @@
       </c>
     </row>
     <row r="745" spans="1:2">
-      <c r="A745" s="2">
+      <c r="A745" s="3">
         <v>44897</v>
       </c>
       <c r="B745">
@@ -6324,7 +6350,7 @@
       </c>
     </row>
     <row r="746" spans="1:2">
-      <c r="A746" s="2">
+      <c r="A746" s="3">
         <v>44904</v>
       </c>
       <c r="B746">
@@ -6332,7 +6358,7 @@
       </c>
     </row>
     <row r="747" spans="1:2">
-      <c r="A747" s="2">
+      <c r="A747" s="3">
         <v>44911</v>
       </c>
       <c r="B747">
@@ -6340,7 +6366,7 @@
       </c>
     </row>
     <row r="748" spans="1:2">
-      <c r="A748" s="2">
+      <c r="A748" s="3">
         <v>44918</v>
       </c>
       <c r="B748">
@@ -6348,7 +6374,7 @@
       </c>
     </row>
     <row r="749" spans="1:2">
-      <c r="A749" s="2">
+      <c r="A749" s="3">
         <v>44925</v>
       </c>
       <c r="B749">
@@ -6356,7 +6382,7 @@
       </c>
     </row>
     <row r="750" spans="1:2">
-      <c r="A750" s="2">
+      <c r="A750" s="3">
         <v>44932</v>
       </c>
       <c r="B750">
@@ -6364,7 +6390,7 @@
       </c>
     </row>
     <row r="751" spans="1:2">
-      <c r="A751" s="2">
+      <c r="A751" s="3">
         <v>44939</v>
       </c>
       <c r="B751">
@@ -6372,7 +6398,7 @@
       </c>
     </row>
     <row r="752" spans="1:2">
-      <c r="A752" s="2">
+      <c r="A752" s="3">
         <v>44946</v>
       </c>
       <c r="B752">
@@ -6380,7 +6406,7 @@
       </c>
     </row>
     <row r="753" spans="1:2">
-      <c r="A753" s="2">
+      <c r="A753" s="3">
         <v>44953</v>
       </c>
       <c r="B753">
@@ -6388,7 +6414,7 @@
       </c>
     </row>
     <row r="754" spans="1:2">
-      <c r="A754" s="2">
+      <c r="A754" s="3">
         <v>44960</v>
       </c>
       <c r="B754">
@@ -6396,7 +6422,7 @@
       </c>
     </row>
     <row r="755" spans="1:2">
-      <c r="A755" s="2">
+      <c r="A755" s="3">
         <v>44967</v>
       </c>
       <c r="B755">
@@ -6404,7 +6430,7 @@
       </c>
     </row>
     <row r="756" spans="1:2">
-      <c r="A756" s="2">
+      <c r="A756" s="3">
         <v>44974</v>
       </c>
       <c r="B756">
@@ -6412,7 +6438,7 @@
       </c>
     </row>
     <row r="757" spans="1:2">
-      <c r="A757" s="2">
+      <c r="A757" s="3">
         <v>44981</v>
       </c>
       <c r="B757">
@@ -6420,7 +6446,7 @@
       </c>
     </row>
     <row r="758" spans="1:2">
-      <c r="A758" s="2">
+      <c r="A758" s="3">
         <v>44988</v>
       </c>
       <c r="B758">
@@ -6428,7 +6454,7 @@
       </c>
     </row>
     <row r="759" spans="1:2">
-      <c r="A759" s="2">
+      <c r="A759" s="3">
         <v>44995</v>
       </c>
       <c r="B759">
@@ -6436,7 +6462,7 @@
       </c>
     </row>
     <row r="760" spans="1:2">
-      <c r="A760" s="2">
+      <c r="A760" s="3">
         <v>45002</v>
       </c>
       <c r="B760">
@@ -6444,7 +6470,7 @@
       </c>
     </row>
     <row r="761" spans="1:2">
-      <c r="A761" s="2">
+      <c r="A761" s="3">
         <v>45009</v>
       </c>
       <c r="B761">
@@ -6452,7 +6478,7 @@
       </c>
     </row>
     <row r="762" spans="1:2">
-      <c r="A762" s="2">
+      <c r="A762" s="3">
         <v>45016</v>
       </c>
       <c r="B762">
@@ -6460,7 +6486,7 @@
       </c>
     </row>
     <row r="763" spans="1:2">
-      <c r="A763" s="2">
+      <c r="A763" s="3">
         <v>45023</v>
       </c>
       <c r="B763">
@@ -6468,7 +6494,7 @@
       </c>
     </row>
     <row r="764" spans="1:2">
-      <c r="A764" s="2">
+      <c r="A764" s="3">
         <v>45030</v>
       </c>
       <c r="B764">
@@ -6476,7 +6502,7 @@
       </c>
     </row>
     <row r="765" spans="1:2">
-      <c r="A765" s="2">
+      <c r="A765" s="3">
         <v>45037</v>
       </c>
       <c r="B765">
@@ -6484,7 +6510,7 @@
       </c>
     </row>
     <row r="766" spans="1:2">
-      <c r="A766" s="2">
+      <c r="A766" s="3">
         <v>45044</v>
       </c>
       <c r="B766">
@@ -6492,7 +6518,7 @@
       </c>
     </row>
     <row r="767" spans="1:2">
-      <c r="A767" s="2">
+      <c r="A767" s="3">
         <v>45051</v>
       </c>
       <c r="B767">
@@ -6500,7 +6526,7 @@
       </c>
     </row>
     <row r="768" spans="1:2">
-      <c r="A768" s="2">
+      <c r="A768" s="3">
         <v>45058</v>
       </c>
       <c r="B768">
@@ -6508,7 +6534,7 @@
       </c>
     </row>
     <row r="769" spans="1:2">
-      <c r="A769" s="2">
+      <c r="A769" s="3">
         <v>45065</v>
       </c>
       <c r="B769">
@@ -6516,7 +6542,7 @@
       </c>
     </row>
     <row r="770" spans="1:2">
-      <c r="A770" s="2">
+      <c r="A770" s="3">
         <v>45072</v>
       </c>
       <c r="B770">
@@ -6524,7 +6550,7 @@
       </c>
     </row>
     <row r="771" spans="1:2">
-      <c r="A771" s="2">
+      <c r="A771" s="3">
         <v>45079</v>
       </c>
       <c r="B771">
@@ -6532,7 +6558,7 @@
       </c>
     </row>
     <row r="772" spans="1:2">
-      <c r="A772" s="2">
+      <c r="A772" s="3">
         <v>45086</v>
       </c>
       <c r="B772">
@@ -6540,7 +6566,7 @@
       </c>
     </row>
     <row r="773" spans="1:2">
-      <c r="A773" s="2">
+      <c r="A773" s="3">
         <v>45093</v>
       </c>
       <c r="B773">
@@ -6548,7 +6574,7 @@
       </c>
     </row>
     <row r="774" spans="1:2">
-      <c r="A774" s="2">
+      <c r="A774" s="3">
         <v>45100</v>
       </c>
       <c r="B774">
@@ -6556,7 +6582,7 @@
       </c>
     </row>
     <row r="775" spans="1:2">
-      <c r="A775" s="2">
+      <c r="A775" s="3">
         <v>45107</v>
       </c>
       <c r="B775">
@@ -6564,7 +6590,7 @@
       </c>
     </row>
     <row r="776" spans="1:2">
-      <c r="A776" s="2">
+      <c r="A776" s="3">
         <v>45114</v>
       </c>
       <c r="B776">
@@ -6572,7 +6598,7 @@
       </c>
     </row>
     <row r="777" spans="1:2">
-      <c r="A777" s="2">
+      <c r="A777" s="3">
         <v>45121</v>
       </c>
       <c r="B777">
@@ -6580,7 +6606,7 @@
       </c>
     </row>
     <row r="778" spans="1:2">
-      <c r="A778" s="2">
+      <c r="A778" s="3">
         <v>45128</v>
       </c>
       <c r="B778">
@@ -6588,7 +6614,7 @@
       </c>
     </row>
     <row r="779" spans="1:2">
-      <c r="A779" s="2">
+      <c r="A779" s="3">
         <v>45135</v>
       </c>
       <c r="B779">
@@ -6596,7 +6622,7 @@
       </c>
     </row>
     <row r="780" spans="1:2">
-      <c r="A780" s="2">
+      <c r="A780" s="3">
         <v>45142</v>
       </c>
       <c r="B780">
@@ -6604,7 +6630,7 @@
       </c>
     </row>
     <row r="781" spans="1:2">
-      <c r="A781" s="2">
+      <c r="A781" s="3">
         <v>45149</v>
       </c>
       <c r="B781">
@@ -6612,7 +6638,7 @@
       </c>
     </row>
     <row r="782" spans="1:2">
-      <c r="A782" s="2">
+      <c r="A782" s="3">
         <v>45156</v>
       </c>
       <c r="B782">
@@ -6620,7 +6646,7 @@
       </c>
     </row>
     <row r="783" spans="1:2">
-      <c r="A783" s="2">
+      <c r="A783" s="3">
         <v>45163</v>
       </c>
       <c r="B783">
@@ -6628,7 +6654,7 @@
       </c>
     </row>
     <row r="784" spans="1:2">
-      <c r="A784" s="2">
+      <c r="A784" s="3">
         <v>45170</v>
       </c>
       <c r="B784">
@@ -6636,7 +6662,7 @@
       </c>
     </row>
     <row r="785" spans="1:2">
-      <c r="A785" s="2">
+      <c r="A785" s="3">
         <v>45177</v>
       </c>
       <c r="B785">
@@ -6644,7 +6670,7 @@
       </c>
     </row>
     <row r="786" spans="1:2">
-      <c r="A786" s="2">
+      <c r="A786" s="3">
         <v>45184</v>
       </c>
       <c r="B786">
@@ -6652,7 +6678,7 @@
       </c>
     </row>
     <row r="787" spans="1:2">
-      <c r="A787" s="2">
+      <c r="A787" s="3">
         <v>45191</v>
       </c>
       <c r="B787">
@@ -6660,7 +6686,7 @@
       </c>
     </row>
     <row r="788" spans="1:2">
-      <c r="A788" s="2">
+      <c r="A788" s="3">
         <v>45198</v>
       </c>
       <c r="B788">
@@ -6668,7 +6694,7 @@
       </c>
     </row>
     <row r="789" spans="1:2">
-      <c r="A789" s="2">
+      <c r="A789" s="3">
         <v>45205</v>
       </c>
       <c r="B789">
@@ -6676,7 +6702,7 @@
       </c>
     </row>
     <row r="790" spans="1:2">
-      <c r="A790" s="2">
+      <c r="A790" s="3">
         <v>45212</v>
       </c>
       <c r="B790">
@@ -6684,7 +6710,7 @@
       </c>
     </row>
     <row r="791" spans="1:2">
-      <c r="A791" s="2">
+      <c r="A791" s="3">
         <v>45219</v>
       </c>
       <c r="B791">
@@ -6692,7 +6718,7 @@
       </c>
     </row>
     <row r="792" spans="1:2">
-      <c r="A792" s="2">
+      <c r="A792" s="3">
         <v>45226</v>
       </c>
       <c r="B792">
@@ -6700,7 +6726,7 @@
       </c>
     </row>
     <row r="793" spans="1:2">
-      <c r="A793" s="2">
+      <c r="A793" s="3">
         <v>45233</v>
       </c>
       <c r="B793">
@@ -6708,7 +6734,7 @@
       </c>
     </row>
     <row r="794" spans="1:2">
-      <c r="A794" s="2">
+      <c r="A794" s="3">
         <v>45240</v>
       </c>
       <c r="B794">
@@ -6716,7 +6742,7 @@
       </c>
     </row>
     <row r="795" spans="1:2">
-      <c r="A795" s="2">
+      <c r="A795" s="3">
         <v>45247</v>
       </c>
       <c r="B795">
@@ -6724,7 +6750,7 @@
       </c>
     </row>
     <row r="796" spans="1:2">
-      <c r="A796" s="2">
+      <c r="A796" s="3">
         <v>45254</v>
       </c>
       <c r="B796">
@@ -6732,7 +6758,7 @@
       </c>
     </row>
     <row r="797" spans="1:2">
-      <c r="A797" s="2">
+      <c r="A797" s="3">
         <v>45261</v>
       </c>
       <c r="B797">
@@ -6740,7 +6766,7 @@
       </c>
     </row>
     <row r="798" spans="1:2">
-      <c r="A798" s="2">
+      <c r="A798" s="3">
         <v>45268</v>
       </c>
       <c r="B798">
@@ -6748,7 +6774,7 @@
       </c>
     </row>
     <row r="799" spans="1:2">
-      <c r="A799" s="2">
+      <c r="A799" s="3">
         <v>45275</v>
       </c>
       <c r="B799">
@@ -6756,7 +6782,7 @@
       </c>
     </row>
     <row r="800" spans="1:2">
-      <c r="A800" s="2">
+      <c r="A800" s="3">
         <v>45282</v>
       </c>
       <c r="B800">
@@ -6764,7 +6790,7 @@
       </c>
     </row>
     <row r="801" spans="1:2">
-      <c r="A801" s="2">
+      <c r="A801" s="3">
         <v>45289</v>
       </c>
       <c r="B801">
@@ -6772,7 +6798,7 @@
       </c>
     </row>
     <row r="802" spans="1:2">
-      <c r="A802" s="2">
+      <c r="A802" s="3">
         <v>45296</v>
       </c>
       <c r="B802">
@@ -6780,7 +6806,7 @@
       </c>
     </row>
     <row r="803" spans="1:2">
-      <c r="A803" s="2">
+      <c r="A803" s="3">
         <v>45303</v>
       </c>
       <c r="B803">
@@ -6788,7 +6814,7 @@
       </c>
     </row>
     <row r="804" spans="1:2">
-      <c r="A804" s="2">
+      <c r="A804" s="3">
         <v>45310</v>
       </c>
       <c r="B804">
@@ -6796,7 +6822,7 @@
       </c>
     </row>
     <row r="805" spans="1:2">
-      <c r="A805" s="2">
+      <c r="A805" s="3">
         <v>45317</v>
       </c>
       <c r="B805">
@@ -6804,7 +6830,7 @@
       </c>
     </row>
     <row r="806" spans="1:2">
-      <c r="A806" s="2">
+      <c r="A806" s="3">
         <v>45324</v>
       </c>
       <c r="B806">
@@ -6812,7 +6838,7 @@
       </c>
     </row>
     <row r="807" spans="1:2">
-      <c r="A807" s="2">
+      <c r="A807" s="3">
         <v>45331</v>
       </c>
       <c r="B807">
@@ -6820,7 +6846,7 @@
       </c>
     </row>
     <row r="808" spans="1:2">
-      <c r="A808" s="2">
+      <c r="A808" s="3">
         <v>45338</v>
       </c>
       <c r="B808">
@@ -6828,7 +6854,7 @@
       </c>
     </row>
     <row r="809" spans="1:2">
-      <c r="A809" s="2">
+      <c r="A809" s="3">
         <v>45345</v>
       </c>
       <c r="B809">
@@ -6836,7 +6862,7 @@
       </c>
     </row>
     <row r="810" spans="1:2">
-      <c r="A810" s="2">
+      <c r="A810" s="3">
         <v>45352</v>
       </c>
       <c r="B810">
@@ -6844,7 +6870,7 @@
       </c>
     </row>
     <row r="811" spans="1:2">
-      <c r="A811" s="2">
+      <c r="A811" s="3">
         <v>45359</v>
       </c>
       <c r="B811">
@@ -6852,7 +6878,7 @@
       </c>
     </row>
     <row r="812" spans="1:2">
-      <c r="A812" s="2">
+      <c r="A812" s="3">
         <v>45366</v>
       </c>
       <c r="B812">
@@ -6860,7 +6886,7 @@
       </c>
     </row>
     <row r="813" spans="1:2">
-      <c r="A813" s="2">
+      <c r="A813" s="3">
         <v>45373</v>
       </c>
       <c r="B813">
@@ -6868,7 +6894,7 @@
       </c>
     </row>
     <row r="814" spans="1:2">
-      <c r="A814" s="2">
+      <c r="A814" s="3">
         <v>45380</v>
       </c>
       <c r="B814">
@@ -6876,7 +6902,7 @@
       </c>
     </row>
     <row r="815" spans="1:2">
-      <c r="A815" s="2">
+      <c r="A815" s="3">
         <v>45387</v>
       </c>
       <c r="B815">
@@ -6884,7 +6910,7 @@
       </c>
     </row>
     <row r="816" spans="1:2">
-      <c r="A816" s="2">
+      <c r="A816" s="3">
         <v>45394</v>
       </c>
       <c r="B816">
@@ -6892,7 +6918,7 @@
       </c>
     </row>
     <row r="817" spans="1:2">
-      <c r="A817" s="2">
+      <c r="A817" s="3">
         <v>45401</v>
       </c>
       <c r="B817">
@@ -6900,7 +6926,7 @@
       </c>
     </row>
     <row r="818" spans="1:2">
-      <c r="A818" s="2">
+      <c r="A818" s="3">
         <v>45408</v>
       </c>
       <c r="B818">
@@ -6908,7 +6934,7 @@
       </c>
     </row>
     <row r="819" spans="1:2">
-      <c r="A819" s="2">
+      <c r="A819" s="3">
         <v>45415</v>
       </c>
       <c r="B819">
@@ -6916,7 +6942,7 @@
       </c>
     </row>
     <row r="820" spans="1:2">
-      <c r="A820" s="2">
+      <c r="A820" s="3">
         <v>45422</v>
       </c>
       <c r="B820">
@@ -6924,7 +6950,7 @@
       </c>
     </row>
     <row r="821" spans="1:2">
-      <c r="A821" s="2">
+      <c r="A821" s="3">
         <v>45429</v>
       </c>
       <c r="B821">
@@ -6932,7 +6958,7 @@
       </c>
     </row>
     <row r="822" spans="1:2">
-      <c r="A822" s="2">
+      <c r="A822" s="3">
         <v>45436</v>
       </c>
       <c r="B822">
@@ -6940,7 +6966,7 @@
       </c>
     </row>
     <row r="823" spans="1:2">
-      <c r="A823" s="2">
+      <c r="A823" s="3">
         <v>45443</v>
       </c>
       <c r="B823">
@@ -6948,7 +6974,7 @@
       </c>
     </row>
     <row r="824" spans="1:2">
-      <c r="A824" s="2">
+      <c r="A824" s="3">
         <v>45450</v>
       </c>
       <c r="B824">
@@ -6956,7 +6982,7 @@
       </c>
     </row>
     <row r="825" spans="1:2">
-      <c r="A825" s="2">
+      <c r="A825" s="3">
         <v>45457</v>
       </c>
       <c r="B825">
@@ -6964,7 +6990,7 @@
       </c>
     </row>
     <row r="826" spans="1:2">
-      <c r="A826" s="2">
+      <c r="A826" s="3">
         <v>45464</v>
       </c>
       <c r="B826">
@@ -6972,7 +6998,7 @@
       </c>
     </row>
     <row r="827" spans="1:2">
-      <c r="A827" s="2">
+      <c r="A827" s="3">
         <v>45471</v>
       </c>
       <c r="B827">
@@ -6980,7 +7006,7 @@
       </c>
     </row>
     <row r="828" spans="1:2">
-      <c r="A828" s="2">
+      <c r="A828" s="3">
         <v>45478</v>
       </c>
       <c r="B828">
@@ -6988,7 +7014,7 @@
       </c>
     </row>
     <row r="829" spans="1:2">
-      <c r="A829" s="2">
+      <c r="A829" s="3">
         <v>45485</v>
       </c>
       <c r="B829">
@@ -6996,7 +7022,7 @@
       </c>
     </row>
     <row r="830" spans="1:2">
-      <c r="A830" s="2">
+      <c r="A830" s="3">
         <v>45492</v>
       </c>
       <c r="B830">
@@ -7004,7 +7030,7 @@
       </c>
     </row>
     <row r="831" spans="1:2">
-      <c r="A831" s="2">
+      <c r="A831" s="3">
         <v>45499</v>
       </c>
       <c r="B831">
@@ -7012,7 +7038,7 @@
       </c>
     </row>
     <row r="832" spans="1:2">
-      <c r="A832" s="2">
+      <c r="A832" s="3">
         <v>45506</v>
       </c>
       <c r="B832">
@@ -7020,7 +7046,7 @@
       </c>
     </row>
     <row r="833" spans="1:2">
-      <c r="A833" s="2">
+      <c r="A833" s="3">
         <v>45513</v>
       </c>
       <c r="B833">
@@ -7028,7 +7054,7 @@
       </c>
     </row>
     <row r="834" spans="1:2">
-      <c r="A834" s="2">
+      <c r="A834" s="3">
         <v>45520</v>
       </c>
       <c r="B834">
@@ -7036,7 +7062,7 @@
       </c>
     </row>
     <row r="835" spans="1:2">
-      <c r="A835" s="2">
+      <c r="A835" s="3">
         <v>45527</v>
       </c>
       <c r="B835">
@@ -7044,7 +7070,7 @@
       </c>
     </row>
     <row r="836" spans="1:2">
-      <c r="A836" s="2">
+      <c r="A836" s="3">
         <v>45534</v>
       </c>
       <c r="B836">
@@ -7052,7 +7078,7 @@
       </c>
     </row>
     <row r="837" spans="1:2">
-      <c r="A837" s="2">
+      <c r="A837" s="3">
         <v>45541</v>
       </c>
       <c r="B837">
@@ -7060,7 +7086,7 @@
       </c>
     </row>
     <row r="838" spans="1:2">
-      <c r="A838" s="2">
+      <c r="A838" s="3">
         <v>45548</v>
       </c>
       <c r="B838">
@@ -7068,7 +7094,7 @@
       </c>
     </row>
     <row r="839" spans="1:2">
-      <c r="A839" s="2">
+      <c r="A839" s="3">
         <v>45555</v>
       </c>
       <c r="B839">
@@ -7076,7 +7102,7 @@
       </c>
     </row>
     <row r="840" spans="1:2">
-      <c r="A840" s="2">
+      <c r="A840" s="3">
         <v>45562</v>
       </c>
       <c r="B840">
@@ -7084,7 +7110,7 @@
       </c>
     </row>
     <row r="841" spans="1:2">
-      <c r="A841" s="2">
+      <c r="A841" s="3">
         <v>45569</v>
       </c>
       <c r="B841">
@@ -7092,7 +7118,7 @@
       </c>
     </row>
     <row r="842" spans="1:2">
-      <c r="A842" s="2">
+      <c r="A842" s="3">
         <v>45576</v>
       </c>
       <c r="B842">
@@ -7100,7 +7126,7 @@
       </c>
     </row>
     <row r="843" spans="1:2">
-      <c r="A843" s="2">
+      <c r="A843" s="3">
         <v>45583</v>
       </c>
       <c r="B843">
@@ -7108,7 +7134,7 @@
       </c>
     </row>
     <row r="844" spans="1:2">
-      <c r="A844" s="2">
+      <c r="A844" s="3">
         <v>45590</v>
       </c>
       <c r="B844">
@@ -7116,7 +7142,7 @@
       </c>
     </row>
     <row r="845" spans="1:2">
-      <c r="A845" s="2">
+      <c r="A845" s="3">
         <v>45597</v>
       </c>
       <c r="B845">
@@ -7124,7 +7150,7 @@
       </c>
     </row>
     <row r="846" spans="1:2">
-      <c r="A846" s="2">
+      <c r="A846" s="3">
         <v>45604</v>
       </c>
       <c r="B846">
@@ -7132,7 +7158,7 @@
       </c>
     </row>
     <row r="847" spans="1:2">
-      <c r="A847" s="2">
+      <c r="A847" s="3">
         <v>45611</v>
       </c>
       <c r="B847">
@@ -7140,7 +7166,7 @@
       </c>
     </row>
     <row r="848" spans="1:2">
-      <c r="A848" s="2">
+      <c r="A848" s="3">
         <v>45618</v>
       </c>
       <c r="B848">
@@ -7148,7 +7174,7 @@
       </c>
     </row>
     <row r="849" spans="1:2">
-      <c r="A849" s="2">
+      <c r="A849" s="3">
         <v>45625</v>
       </c>
       <c r="B849">
@@ -7156,7 +7182,7 @@
       </c>
     </row>
     <row r="850" spans="1:2">
-      <c r="A850" s="2">
+      <c r="A850" s="3">
         <v>45632</v>
       </c>
       <c r="B850">
@@ -7164,7 +7190,7 @@
       </c>
     </row>
     <row r="851" spans="1:2">
-      <c r="A851" s="2">
+      <c r="A851" s="3">
         <v>45639</v>
       </c>
       <c r="B851">
@@ -7172,7 +7198,7 @@
       </c>
     </row>
     <row r="852" spans="1:2">
-      <c r="A852" s="2">
+      <c r="A852" s="3">
         <v>45646</v>
       </c>
       <c r="B852">
@@ -7180,7 +7206,7 @@
       </c>
     </row>
     <row r="853" spans="1:2">
-      <c r="A853" s="2">
+      <c r="A853" s="3">
         <v>45653</v>
       </c>
       <c r="B853">
@@ -7188,7 +7214,7 @@
       </c>
     </row>
     <row r="854" spans="1:2">
-      <c r="A854" s="2">
+      <c r="A854" s="3">
         <v>45660</v>
       </c>
       <c r="B854">
@@ -7196,7 +7222,7 @@
       </c>
     </row>
     <row r="855" spans="1:2">
-      <c r="A855" s="2">
+      <c r="A855" s="3">
         <v>45667</v>
       </c>
       <c r="B855">
@@ -7204,7 +7230,7 @@
       </c>
     </row>
     <row r="856" spans="1:2">
-      <c r="A856" s="2">
+      <c r="A856" s="3">
         <v>45674</v>
       </c>
       <c r="B856">
@@ -7212,7 +7238,7 @@
       </c>
     </row>
     <row r="857" spans="1:2">
-      <c r="A857" s="2">
+      <c r="A857" s="3">
         <v>45681</v>
       </c>
       <c r="B857">
@@ -7220,7 +7246,7 @@
       </c>
     </row>
     <row r="858" spans="1:2">
-      <c r="A858" s="2">
+      <c r="A858" s="3">
         <v>45688</v>
       </c>
       <c r="B858">
@@ -7228,7 +7254,7 @@
       </c>
     </row>
     <row r="859" spans="1:2">
-      <c r="A859" s="2">
+      <c r="A859" s="3">
         <v>45695</v>
       </c>
       <c r="B859">
@@ -7236,7 +7262,7 @@
       </c>
     </row>
     <row r="860" spans="1:2">
-      <c r="A860" s="2">
+      <c r="A860" s="3">
         <v>45702</v>
       </c>
       <c r="B860">
@@ -7244,7 +7270,7 @@
       </c>
     </row>
     <row r="861" spans="1:2">
-      <c r="A861" s="2">
+      <c r="A861" s="3">
         <v>45709</v>
       </c>
       <c r="B861">
@@ -7252,7 +7278,7 @@
       </c>
     </row>
     <row r="862" spans="1:2">
-      <c r="A862" s="2">
+      <c r="A862" s="3">
         <v>45716</v>
       </c>
       <c r="B862">
@@ -7260,7 +7286,7 @@
       </c>
     </row>
     <row r="863" spans="1:2">
-      <c r="A863" s="2">
+      <c r="A863" s="3">
         <v>45723</v>
       </c>
       <c r="B863">
@@ -7268,7 +7294,7 @@
       </c>
     </row>
     <row r="864" spans="1:2">
-      <c r="A864" s="2">
+      <c r="A864" s="3">
         <v>45730</v>
       </c>
       <c r="B864">
@@ -7276,7 +7302,7 @@
       </c>
     </row>
     <row r="865" spans="1:2">
-      <c r="A865" s="2">
+      <c r="A865" s="3">
         <v>45737</v>
       </c>
       <c r="B865">
@@ -7284,7 +7310,7 @@
       </c>
     </row>
     <row r="866" spans="1:2">
-      <c r="A866" s="2">
+      <c r="A866" s="3">
         <v>45744</v>
       </c>
       <c r="B866">
@@ -7292,7 +7318,7 @@
       </c>
     </row>
     <row r="867" spans="1:2">
-      <c r="A867" s="2">
+      <c r="A867" s="3">
         <v>45751</v>
       </c>
       <c r="B867">
@@ -7300,7 +7326,7 @@
       </c>
     </row>
     <row r="868" spans="1:2">
-      <c r="A868" s="2">
+      <c r="A868" s="3">
         <v>45758</v>
       </c>
       <c r="B868">
@@ -7308,7 +7334,7 @@
       </c>
     </row>
     <row r="869" spans="1:2">
-      <c r="A869" s="2">
+      <c r="A869" s="3">
         <v>45765</v>
       </c>
       <c r="B869">
@@ -7316,7 +7342,7 @@
       </c>
     </row>
     <row r="870" spans="1:2">
-      <c r="A870" s="2">
+      <c r="A870" s="3">
         <v>45772</v>
       </c>
       <c r="B870">
@@ -7324,7 +7350,7 @@
       </c>
     </row>
     <row r="871" spans="1:2">
-      <c r="A871" s="2">
+      <c r="A871" s="3">
         <v>45779</v>
       </c>
       <c r="B871">
@@ -7332,7 +7358,7 @@
       </c>
     </row>
     <row r="872" spans="1:2">
-      <c r="A872" s="2">
+      <c r="A872" s="3">
         <v>45786</v>
       </c>
       <c r="B872">
@@ -7340,7 +7366,7 @@
       </c>
     </row>
     <row r="873" spans="1:2">
-      <c r="A873" s="2">
+      <c r="A873" s="3">
         <v>45793</v>
       </c>
       <c r="B873">
@@ -7348,7 +7374,7 @@
       </c>
     </row>
     <row r="874" spans="1:2">
-      <c r="A874" s="2">
+      <c r="A874" s="3">
         <v>45800</v>
       </c>
       <c r="B874">
@@ -7356,7 +7382,7 @@
       </c>
     </row>
     <row r="875" spans="1:2">
-      <c r="A875" s="2">
+      <c r="A875" s="3">
         <v>45807</v>
       </c>
       <c r="B875">
@@ -7364,7 +7390,7 @@
       </c>
     </row>
     <row r="876" spans="1:2">
-      <c r="A876" s="2">
+      <c r="A876" s="3">
         <v>45814</v>
       </c>
       <c r="B876">
@@ -7372,7 +7398,7 @@
       </c>
     </row>
     <row r="877" spans="1:2">
-      <c r="A877" s="2">
+      <c r="A877" s="3">
         <v>45821</v>
       </c>
       <c r="B877">
@@ -7380,7 +7406,7 @@
       </c>
     </row>
     <row r="878" spans="1:2">
-      <c r="A878" s="2">
+      <c r="A878" s="3">
         <v>45828</v>
       </c>
       <c r="B878">
@@ -7388,7 +7414,7 @@
       </c>
     </row>
     <row r="879" spans="1:2">
-      <c r="A879" s="2">
+      <c r="A879" s="3">
         <v>45835</v>
       </c>
       <c r="B879">
@@ -7396,7 +7422,7 @@
       </c>
     </row>
     <row r="880" spans="1:2">
-      <c r="A880" s="2">
+      <c r="A880" s="3">
         <v>45842</v>
       </c>
       <c r="B880">
@@ -7404,7 +7430,7 @@
       </c>
     </row>
     <row r="881" spans="1:2">
-      <c r="A881" s="2">
+      <c r="A881" s="3">
         <v>45849</v>
       </c>
       <c r="B881">
@@ -7412,7 +7438,7 @@
       </c>
     </row>
     <row r="882" spans="1:2">
-      <c r="A882" s="2">
+      <c r="A882" s="3">
         <v>45856</v>
       </c>
       <c r="B882">
@@ -7420,7 +7446,7 @@
       </c>
     </row>
     <row r="883" spans="1:2">
-      <c r="A883" s="2">
+      <c r="A883" s="3">
         <v>45863</v>
       </c>
       <c r="B883">
@@ -7428,7 +7454,7 @@
       </c>
     </row>
     <row r="884" spans="1:2">
-      <c r="A884" s="2">
+      <c r="A884" s="3">
         <v>45870</v>
       </c>
       <c r="B884">
@@ -7436,7 +7462,7 @@
       </c>
     </row>
     <row r="885" spans="1:2">
-      <c r="A885" s="2">
+      <c r="A885" s="3">
         <v>45877</v>
       </c>
       <c r="B885">
@@ -7444,7 +7470,7 @@
       </c>
     </row>
     <row r="886" spans="1:2">
-      <c r="A886" s="2">
+      <c r="A886" s="3">
         <v>45884</v>
       </c>
       <c r="B886">
@@ -7452,7 +7478,7 @@
       </c>
     </row>
     <row r="887" spans="1:2">
-      <c r="A887" s="2">
+      <c r="A887" s="3">
         <v>45891</v>
       </c>
       <c r="B887">
@@ -7460,7 +7486,7 @@
       </c>
     </row>
     <row r="888" spans="1:2">
-      <c r="A888" s="2">
+      <c r="A888" s="3">
         <v>45898</v>
       </c>
       <c r="B888">
@@ -7468,7 +7494,7 @@
       </c>
     </row>
     <row r="889" spans="1:2">
-      <c r="A889" s="2">
+      <c r="A889" s="3">
         <v>45905</v>
       </c>
       <c r="B889">
@@ -7476,7 +7502,7 @@
       </c>
     </row>
     <row r="890" spans="1:2">
-      <c r="A890" s="2">
+      <c r="A890" s="3">
         <v>45912</v>
       </c>
       <c r="B890">
@@ -7484,7 +7510,7 @@
       </c>
     </row>
     <row r="891" spans="1:2">
-      <c r="A891" s="2">
+      <c r="A891" s="3">
         <v>45919</v>
       </c>
       <c r="B891">
@@ -7492,7 +7518,7 @@
       </c>
     </row>
     <row r="892" spans="1:2">
-      <c r="A892" s="2">
+      <c r="A892" s="3">
         <v>45926</v>
       </c>
       <c r="B892">
@@ -7500,7 +7526,7 @@
       </c>
     </row>
     <row r="893" spans="1:2">
-      <c r="A893" s="2">
+      <c r="A893" s="3">
         <v>45933</v>
       </c>
       <c r="B893">
@@ -7508,7 +7534,7 @@
       </c>
     </row>
     <row r="894" spans="1:2">
-      <c r="A894" s="2">
+      <c r="A894" s="3">
         <v>45940</v>
       </c>
       <c r="B894">
@@ -7516,7 +7542,7 @@
       </c>
     </row>
     <row r="895" spans="1:2">
-      <c r="A895" s="2">
+      <c r="A895" s="3">
         <v>45947</v>
       </c>
       <c r="B895">
@@ -7524,7 +7550,7 @@
       </c>
     </row>
     <row r="896" spans="1:2">
-      <c r="A896" s="2">
+      <c r="A896" s="3">
         <v>45954</v>
       </c>
       <c r="B896">
@@ -7532,7 +7558,7 @@
       </c>
     </row>
     <row r="897" spans="1:2">
-      <c r="A897" s="2">
+      <c r="A897" s="3">
         <v>45961</v>
       </c>
       <c r="B897">
@@ -7540,7 +7566,7 @@
       </c>
     </row>
     <row r="898" spans="1:2">
-      <c r="A898" s="2">
+      <c r="A898" s="3">
         <v>45968</v>
       </c>
       <c r="B898">
@@ -7548,7 +7574,7 @@
       </c>
     </row>
     <row r="899" spans="1:2">
-      <c r="A899" s="2">
+      <c r="A899" s="3">
         <v>45975</v>
       </c>
       <c r="B899">
@@ -7556,7 +7582,7 @@
       </c>
     </row>
     <row r="900" spans="1:2">
-      <c r="A900" s="2">
+      <c r="A900" s="3">
         <v>45982</v>
       </c>
       <c r="B900">
@@ -7564,7 +7590,7 @@
       </c>
     </row>
     <row r="901" spans="1:2">
-      <c r="A901" s="2">
+      <c r="A901" s="3">
         <v>45989</v>
       </c>
       <c r="B901">
@@ -7572,7 +7598,7 @@
       </c>
     </row>
     <row r="902" spans="1:2">
-      <c r="A902" s="2">
+      <c r="A902" s="3">
         <v>45996</v>
       </c>
       <c r="B902">
@@ -7580,7 +7606,7 @@
       </c>
     </row>
     <row r="903" spans="1:2">
-      <c r="A903" s="2">
+      <c r="A903" s="3">
         <v>46003</v>
       </c>
       <c r="B903">
@@ -7588,7 +7614,7 @@
       </c>
     </row>
     <row r="904" spans="1:2">
-      <c r="A904" s="2">
+      <c r="A904" s="3">
         <v>46010</v>
       </c>
       <c r="B904">
@@ -7596,7 +7622,7 @@
       </c>
     </row>
     <row r="905" spans="1:2">
-      <c r="A905" s="2">
+      <c r="A905" s="3">
         <v>46017</v>
       </c>
       <c r="B905">
@@ -7604,7 +7630,7 @@
       </c>
     </row>
     <row r="906" spans="1:2">
-      <c r="A906" s="2">
+      <c r="A906" s="3">
         <v>46024</v>
       </c>
       <c r="B906">
@@ -7612,7 +7638,7 @@
       </c>
     </row>
     <row r="907" spans="1:2">
-      <c r="A907" s="2">
+      <c r="A907" s="3">
         <v>46031</v>
       </c>
       <c r="B907">
@@ -7620,7 +7646,7 @@
       </c>
     </row>
     <row r="908" spans="1:2">
-      <c r="A908" s="2">
+      <c r="A908" s="3">
         <v>46038</v>
       </c>
       <c r="B908">
@@ -7628,7 +7654,7 @@
       </c>
     </row>
     <row r="909" spans="1:2">
-      <c r="A909" s="2">
+      <c r="A909" s="3">
         <v>46045</v>
       </c>
       <c r="B909">
@@ -7636,7 +7662,7 @@
       </c>
     </row>
     <row r="910" spans="1:2">
-      <c r="A910" s="2">
+      <c r="A910" s="3">
         <v>46052</v>
       </c>
       <c r="B910">
@@ -7644,7 +7670,7 @@
       </c>
     </row>
     <row r="911" spans="1:2">
-      <c r="A911" s="2">
+      <c r="A911" s="3">
         <v>46059</v>
       </c>
       <c r="B911">
@@ -7652,7 +7678,7 @@
       </c>
     </row>
     <row r="912" spans="1:2">
-      <c r="A912" s="2">
+      <c r="A912" s="3">
         <v>46066</v>
       </c>
       <c r="B912">
@@ -7660,7 +7686,7 @@
       </c>
     </row>
     <row r="913" spans="1:2">
-      <c r="A913" s="2">
+      <c r="A913" s="3">
         <v>46073</v>
       </c>
       <c r="B913">
@@ -7668,7 +7694,7 @@
       </c>
     </row>
     <row r="914" spans="1:2">
-      <c r="A914" s="2">
+      <c r="A914" s="3">
         <v>46080</v>
       </c>
       <c r="B914">
@@ -7676,7 +7702,7 @@
       </c>
     </row>
     <row r="915" spans="1:2">
-      <c r="A915" s="2">
+      <c r="A915" s="3">
         <v>46087</v>
       </c>
       <c r="B915">
@@ -7684,7 +7710,7 @@
       </c>
     </row>
     <row r="916" spans="1:2">
-      <c r="A916" s="2">
+      <c r="A916" s="3">
         <v>46094</v>
       </c>
       <c r="B916">
@@ -7692,7 +7718,7 @@
       </c>
     </row>
     <row r="917" spans="1:2">
-      <c r="A917" s="2">
+      <c r="A917" s="3">
         <v>46101</v>
       </c>
       <c r="B917">
@@ -7700,7 +7726,7 @@
       </c>
     </row>
     <row r="918" spans="1:2">
-      <c r="A918" s="2">
+      <c r="A918" s="3">
         <v>46108</v>
       </c>
       <c r="B918">
@@ -7708,7 +7734,7 @@
       </c>
     </row>
     <row r="919" spans="1:2">
-      <c r="A919" s="2">
+      <c r="A919" s="3">
         <v>46115</v>
       </c>
       <c r="B919">
@@ -7716,7 +7742,7 @@
       </c>
     </row>
     <row r="920" spans="1:2">
-      <c r="A920" s="2">
+      <c r="A920" s="3">
         <v>46122</v>
       </c>
       <c r="B920">
@@ -7724,7 +7750,7 @@
       </c>
     </row>
     <row r="921" spans="1:2">
-      <c r="A921" s="2">
+      <c r="A921" s="3">
         <v>46129</v>
       </c>
       <c r="B921">
@@ -7732,7 +7758,7 @@
       </c>
     </row>
     <row r="922" spans="1:2">
-      <c r="A922" s="2">
+      <c r="A922" s="3">
         <v>46136</v>
       </c>
       <c r="B922">
@@ -7740,7 +7766,7 @@
       </c>
     </row>
     <row r="923" spans="1:2">
-      <c r="A923" s="2">
+      <c r="A923" s="3">
         <v>46143</v>
       </c>
       <c r="B923">
@@ -7748,7 +7774,7 @@
       </c>
     </row>
     <row r="924" spans="1:2">
-      <c r="A924" s="2">
+      <c r="A924" s="3">
         <v>46150</v>
       </c>
       <c r="B924">
@@ -7756,7 +7782,7 @@
       </c>
     </row>
     <row r="925" spans="1:2">
-      <c r="A925" s="2">
+      <c r="A925" s="3">
         <v>46157</v>
       </c>
       <c r="B925">
@@ -7764,7 +7790,7 @@
       </c>
     </row>
     <row r="926" spans="1:2">
-      <c r="A926" s="2">
+      <c r="A926" s="3">
         <v>46164</v>
       </c>
       <c r="B926">
@@ -7772,7 +7798,7 @@
       </c>
     </row>
     <row r="927" spans="1:2">
-      <c r="A927" s="2">
+      <c r="A927" s="3">
         <v>46171</v>
       </c>
       <c r="B927">
@@ -7780,7 +7806,7 @@
       </c>
     </row>
     <row r="928" spans="1:2">
-      <c r="A928" s="2">
+      <c r="A928" s="3">
         <v>46178</v>
       </c>
       <c r="B928">
@@ -7788,11 +7814,19 @@
       </c>
     </row>
     <row r="929" spans="1:2">
-      <c r="A929" s="2">
+      <c r="A929" s="3">
         <v>46185</v>
       </c>
       <c r="B929">
         <v>4.76339</v>
+      </c>
+    </row>
+    <row r="930" spans="1:2">
+      <c r="A930" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B930">
+        <v>4.75535</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B930"/>
+  <dimension ref="A1:B931"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7829,6 +7829,14 @@
         <v>4.75535</v>
       </c>
     </row>
+    <row r="931" spans="1:2">
+      <c r="A931" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B931">
+        <v>4.69327</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B931"/>
+  <dimension ref="A1:B933"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7837,6 +7837,22 @@
         <v>4.69327</v>
       </c>
     </row>
+    <row r="932" spans="1:2">
+      <c r="A932" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B932">
+        <v>4.70817</v>
+      </c>
+    </row>
+    <row r="933" spans="1:2">
+      <c r="A933" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B933">
+        <v>4.713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B933"/>
+  <dimension ref="A1:B934"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7853,6 +7853,14 @@
         <v>4.713</v>
       </c>
     </row>
+    <row r="934" spans="1:2">
+      <c r="A934" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B934">
+        <v>4.69175</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7858,7 +7858,7 @@
         <v>46220</v>
       </c>
       <c r="B934">
-        <v>4.69175</v>
+        <v>4.72342</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7858,7 +7858,7 @@
         <v>46220</v>
       </c>
       <c r="B934">
-        <v>4.72342</v>
+        <v>4.74173</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7858,7 +7858,7 @@
         <v>46220</v>
       </c>
       <c r="B934">
-        <v>4.74173</v>
+        <v>4.73111</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B934"/>
+  <dimension ref="A1:B935"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7861,6 +7861,14 @@
         <v>4.73111</v>
       </c>
     </row>
+    <row r="935" spans="1:2">
+      <c r="A935" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B935">
+        <v>4.73382</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7866,7 +7866,7 @@
         <v>46227</v>
       </c>
       <c r="B935">
-        <v>4.73382</v>
+        <v>4.73606</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7866,7 +7866,7 @@
         <v>46227</v>
       </c>
       <c r="B935">
-        <v>4.73606</v>
+        <v>4.73979</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7866,7 +7866,7 @@
         <v>46227</v>
       </c>
       <c r="B935">
-        <v>4.73979</v>
+        <v>4.72195</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7866,7 +7866,7 @@
         <v>46227</v>
       </c>
       <c r="B935">
-        <v>4.72195</v>
+        <v>4.7259</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B935"/>
+  <dimension ref="A1:B936"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7869,6 +7869,14 @@
         <v>4.7259</v>
       </c>
     </row>
+    <row r="936" spans="1:2">
+      <c r="A936" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B936">
+        <v>4.7282</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7874,7 +7874,7 @@
         <v>46234</v>
       </c>
       <c r="B936">
-        <v>4.7282</v>
+        <v>4.72079</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7874,7 +7874,7 @@
         <v>46234</v>
       </c>
       <c r="B936">
-        <v>4.72079</v>
+        <v>4.70125</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7874,7 +7874,7 @@
         <v>46234</v>
       </c>
       <c r="B936">
-        <v>4.70125</v>
+        <v>4.74093</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B936"/>
+  <dimension ref="A1:B937"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7877,6 +7877,14 @@
         <v>4.74093</v>
       </c>
     </row>
+    <row r="937" spans="1:2">
+      <c r="A937" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B937">
+        <v>4.72932</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7882,7 +7882,7 @@
         <v>46241</v>
       </c>
       <c r="B937">
-        <v>4.72932</v>
+        <v>4.75301</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7882,7 +7882,7 @@
         <v>46241</v>
       </c>
       <c r="B937">
-        <v>4.75301</v>
+        <v>4.76213</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7882,7 +7882,7 @@
         <v>46241</v>
       </c>
       <c r="B937">
-        <v>4.76213</v>
+        <v>4.74391</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7882,7 +7882,7 @@
         <v>46241</v>
       </c>
       <c r="B937">
-        <v>4.74391</v>
+        <v>4.76528</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B937"/>
+  <dimension ref="A1:B938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7885,6 +7885,14 @@
         <v>4.76528</v>
       </c>
     </row>
+    <row r="938" spans="1:2">
+      <c r="A938" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B938">
+        <v>4.75742</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7890,7 +7890,7 @@
         <v>46248</v>
       </c>
       <c r="B938">
-        <v>4.75742</v>
+        <v>4.76282</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7890,7 +7890,7 @@
         <v>46248</v>
       </c>
       <c r="B938">
-        <v>4.76282</v>
+        <v>4.76275</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7890,7 +7890,7 @@
         <v>46248</v>
       </c>
       <c r="B938">
-        <v>4.76275</v>
+        <v>4.75729</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7890,7 +7890,7 @@
         <v>46248</v>
       </c>
       <c r="B938">
-        <v>4.75729</v>
+        <v>4.77564</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B938"/>
+  <dimension ref="A1:B939"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7893,6 +7893,14 @@
         <v>4.77564</v>
       </c>
     </row>
+    <row r="939" spans="1:2">
+      <c r="A939" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B939">
+        <v>4.78877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7898,7 +7898,7 @@
         <v>46255</v>
       </c>
       <c r="B939">
-        <v>4.78877</v>
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7898,7 +7898,7 @@
         <v>46255</v>
       </c>
       <c r="B939">
-        <v>4.78</v>
+        <v>4.79463</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7898,7 +7898,7 @@
         <v>46255</v>
       </c>
       <c r="B939">
-        <v>4.79463</v>
+        <v>4.78158</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7898,7 +7898,7 @@
         <v>46255</v>
       </c>
       <c r="B939">
-        <v>4.78158</v>
+        <v>4.81707</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B939"/>
+  <dimension ref="A1:B940"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7901,6 +7901,14 @@
         <v>4.81707</v>
       </c>
     </row>
+    <row r="940" spans="1:2">
+      <c r="A940" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B940">
+        <v>4.80441</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7906,7 +7906,7 @@
         <v>46262</v>
       </c>
       <c r="B940">
-        <v>4.80441</v>
+        <v>4.80916</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7906,7 +7906,7 @@
         <v>46262</v>
       </c>
       <c r="B940">
-        <v>4.80916</v>
+        <v>4.81737</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7906,7 +7906,7 @@
         <v>46262</v>
       </c>
       <c r="B940">
-        <v>4.81737</v>
+        <v>4.83329</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7906,7 +7906,7 @@
         <v>46262</v>
       </c>
       <c r="B940">
-        <v>4.83329</v>
+        <v>4.81815</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B940"/>
+  <dimension ref="A1:B941"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -7909,6 +7909,14 @@
         <v>4.81815</v>
       </c>
     </row>
+    <row r="941" spans="1:2">
+      <c r="A941" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B941">
+        <v>4.81398</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7914,7 +7914,7 @@
         <v>46269</v>
       </c>
       <c r="B941">
-        <v>4.81398</v>
+        <v>4.80227</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7914,7 +7914,7 @@
         <v>46269</v>
       </c>
       <c r="B941">
-        <v>4.80227</v>
+        <v>4.81532</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7914,7 +7914,7 @@
         <v>46269</v>
       </c>
       <c r="B941">
-        <v>4.81532</v>
+        <v>4.836</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/AUDCNH_diff_0th_diff.xlsx
@@ -7914,7 +7914,7 @@
         <v>46269</v>
       </c>
       <c r="B941">
-        <v>4.836</v>
+        <v>4.83103</v>
       </c>
     </row>
   </sheetData>
